--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5541FD29-BC27-4C34-BE59-09FD0064C79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3D13A5-2286-40DA-B7D8-C7DD6D5C1201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="-21710" windowWidth="38620" windowHeight="21360" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10233,6 +10233,9 @@
       <c r="B659" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="C659" s="6">
+        <v>5</v>
+      </c>
       <c r="D659" t="s">
         <v>140</v>
       </c>
@@ -10243,6 +10246,9 @@
       </c>
       <c r="B660" s="3" t="s">
         <v>23</v>
+      </c>
+      <c r="C660" s="6">
+        <v>5</v>
       </c>
       <c r="D660" t="s">
         <v>140</v>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3D13A5-2286-40DA-B7D8-C7DD6D5C1201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B11EBB-97A9-4C91-9AB0-4110DCD85C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="337">
   <si>
     <t>BGC10</t>
   </si>
@@ -1024,6 +1024,18 @@
   </si>
   <si>
     <t>FF10oz</t>
+  </si>
+  <si>
+    <t>Habitat PRO-BC-10lbs</t>
+  </si>
+  <si>
+    <t>Habitat PRO-BC-25lbs</t>
+  </si>
+  <si>
+    <t>Habitat PRO-RS-10lbs</t>
+  </si>
+  <si>
+    <t>Habitat PRO-RS-25lbs</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K681"/>
+  <dimension ref="A1:K685"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -7325,10 +7337,10 @@
         <v>181</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>193</v>
+        <v>335</v>
       </c>
       <c r="C419" s="6">
-        <v>11.49</v>
+        <v>15.99</v>
       </c>
       <c r="D419" t="s">
         <v>144</v>
@@ -7339,10 +7351,10 @@
         <v>181</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>194</v>
+        <v>336</v>
       </c>
       <c r="C420" s="6">
-        <v>18.95</v>
+        <v>29.99</v>
       </c>
       <c r="D420" t="s">
         <v>144</v>
@@ -7353,10 +7365,10 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>195</v>
+        <v>333</v>
       </c>
       <c r="C421" s="6">
-        <v>39.99</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D421" t="s">
         <v>144</v>
@@ -7366,11 +7378,11 @@
       <c r="A422" t="s">
         <v>181</v>
       </c>
-      <c r="B422" s="3">
-        <v>6102</v>
+      <c r="B422" s="3" t="s">
+        <v>334</v>
       </c>
       <c r="C422" s="6">
-        <v>44.5</v>
+        <v>29.99</v>
       </c>
       <c r="D422" t="s">
         <v>144</v>
@@ -7381,10 +7393,10 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C423" s="6">
-        <v>112</v>
+        <v>11.49</v>
       </c>
       <c r="D423" t="s">
         <v>144</v>
@@ -7395,10 +7407,10 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C424" s="6">
-        <v>139</v>
+        <v>18.95</v>
       </c>
       <c r="D424" t="s">
         <v>144</v>
@@ -7409,10 +7421,10 @@
         <v>181</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C425" s="6">
-        <v>139</v>
+        <v>39.99</v>
       </c>
       <c r="D425" t="s">
         <v>144</v>
@@ -7422,8 +7434,11 @@
       <c r="A426" t="s">
         <v>181</v>
       </c>
-      <c r="B426" s="3" t="s">
-        <v>199</v>
+      <c r="B426" s="3">
+        <v>6102</v>
+      </c>
+      <c r="C426" s="6">
+        <v>44.5</v>
       </c>
       <c r="D426" t="s">
         <v>144</v>
@@ -7434,7 +7449,10 @@
         <v>181</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
+      </c>
+      <c r="C427" s="6">
+        <v>112</v>
       </c>
       <c r="D427" t="s">
         <v>144</v>
@@ -7445,10 +7463,10 @@
         <v>181</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C428" s="6">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="D428" t="s">
         <v>144</v>
@@ -7459,7 +7477,10 @@
         <v>181</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
+      </c>
+      <c r="C429" s="6">
+        <v>139</v>
       </c>
       <c r="D429" t="s">
         <v>144</v>
@@ -7470,7 +7491,7 @@
         <v>181</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D430" t="s">
         <v>144</v>
@@ -7481,10 +7502,7 @@
         <v>181</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C431" s="6">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="D431" t="s">
         <v>144</v>
@@ -7495,10 +7513,10 @@
         <v>181</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C432" s="6">
-        <v>299.99</v>
+        <v>209</v>
       </c>
       <c r="D432" t="s">
         <v>144</v>
@@ -7509,10 +7527,7 @@
         <v>181</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C433" s="6">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="D433" t="s">
         <v>144</v>
@@ -7523,10 +7538,7 @@
         <v>181</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C434" s="6">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="D434" t="s">
         <v>144</v>
@@ -7537,10 +7549,10 @@
         <v>181</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C435" s="6">
-        <v>240</v>
+        <v>179</v>
       </c>
       <c r="D435" t="s">
         <v>144</v>
@@ -7551,10 +7563,10 @@
         <v>181</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C436" s="6">
-        <v>399</v>
+        <v>299.99</v>
       </c>
       <c r="D436" t="s">
         <v>144</v>
@@ -7565,10 +7577,10 @@
         <v>181</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C437" s="6">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="D437" t="s">
         <v>144</v>
@@ -7579,10 +7591,10 @@
         <v>181</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C438" s="6">
-        <v>345</v>
+        <v>245</v>
       </c>
       <c r="D438" t="s">
         <v>144</v>
@@ -7593,10 +7605,10 @@
         <v>181</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C439" s="6">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D439" t="s">
         <v>144</v>
@@ -7607,10 +7619,10 @@
         <v>181</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C440" s="6">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="D440" t="s">
         <v>144</v>
@@ -7621,10 +7633,10 @@
         <v>181</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C441" s="6">
-        <v>315</v>
+        <v>209</v>
       </c>
       <c r="D441" t="s">
         <v>144</v>
@@ -7635,10 +7647,10 @@
         <v>181</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C442" s="6">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="D442" t="s">
         <v>144</v>
@@ -7649,10 +7661,10 @@
         <v>181</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C443" s="6">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="D443" t="s">
         <v>144</v>
@@ -7663,10 +7675,10 @@
         <v>181</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C444" s="6">
-        <v>420</v>
+        <v>369</v>
       </c>
       <c r="D444" t="s">
         <v>144</v>
@@ -7677,7 +7689,7 @@
         <v>181</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C445" s="6">
         <v>315</v>
@@ -7691,10 +7703,10 @@
         <v>181</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C446" s="6">
-        <v>365</v>
+        <v>265</v>
       </c>
       <c r="D446" t="s">
         <v>144</v>
@@ -7705,10 +7717,10 @@
         <v>181</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C447" s="6">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="D447" t="s">
         <v>144</v>
@@ -7719,13 +7731,13 @@
         <v>181</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="C448" s="6">
-        <v>55.99</v>
+        <v>420</v>
       </c>
       <c r="D448" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -7733,13 +7745,13 @@
         <v>181</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>56</v>
+        <v>218</v>
       </c>
       <c r="C449" s="6">
-        <v>39.99</v>
+        <v>315</v>
       </c>
       <c r="D449" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
@@ -7747,13 +7759,13 @@
         <v>181</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="C450" s="6">
-        <v>68</v>
+        <v>365</v>
       </c>
       <c r="D450" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
@@ -7761,13 +7773,13 @@
         <v>181</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>58</v>
+        <v>220</v>
       </c>
       <c r="C451" s="6">
-        <v>129</v>
+        <v>285</v>
       </c>
       <c r="D451" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
@@ -7775,10 +7787,10 @@
         <v>181</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="C452" s="6">
-        <v>30.99</v>
+        <v>55.99</v>
       </c>
       <c r="D452" t="s">
         <v>145</v>
@@ -7789,10 +7801,10 @@
         <v>181</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="C453" s="6">
-        <v>42.99</v>
+        <v>39.99</v>
       </c>
       <c r="D453" t="s">
         <v>145</v>
@@ -7803,10 +7815,10 @@
         <v>181</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="C454" s="6">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="D454" t="s">
         <v>145</v>
@@ -7817,10 +7829,10 @@
         <v>181</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>274</v>
+        <v>58</v>
       </c>
       <c r="C455" s="6">
-        <v>49.99</v>
+        <v>129</v>
       </c>
       <c r="D455" t="s">
         <v>145</v>
@@ -7831,10 +7843,10 @@
         <v>181</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C456" s="6">
-        <v>129</v>
+        <v>30.99</v>
       </c>
       <c r="D456" t="s">
         <v>145</v>
@@ -7845,13 +7857,13 @@
         <v>181</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="C457" s="6">
-        <v>47.99</v>
+        <v>42.99</v>
       </c>
       <c r="D457" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -7859,13 +7871,13 @@
         <v>181</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="C458" s="6">
-        <v>34.99</v>
+        <v>159</v>
       </c>
       <c r="D458" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -7873,13 +7885,13 @@
         <v>181</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>93</v>
+        <v>274</v>
       </c>
       <c r="C459" s="6">
-        <v>89.99</v>
+        <v>49.99</v>
       </c>
       <c r="D459" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -7887,13 +7899,13 @@
         <v>181</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>180</v>
+        <v>275</v>
       </c>
       <c r="C460" s="6">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="D460" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -7901,13 +7913,13 @@
         <v>181</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="C461" s="6">
-        <v>88</v>
+        <v>47.99</v>
       </c>
       <c r="D461" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -7915,13 +7927,13 @@
         <v>181</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C462" s="6">
-        <v>125</v>
+        <v>34.99</v>
       </c>
       <c r="D462" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -7929,13 +7941,13 @@
         <v>181</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C463" s="6">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="D463" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -7943,13 +7955,13 @@
         <v>181</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>280</v>
+        <v>180</v>
       </c>
       <c r="C464" s="6">
-        <v>7.95</v>
+        <v>45</v>
       </c>
       <c r="D464" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -7957,13 +7969,13 @@
         <v>181</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>277</v>
+        <v>222</v>
       </c>
       <c r="C465" s="6">
-        <v>18.95</v>
+        <v>88</v>
       </c>
       <c r="D465" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -7971,13 +7983,13 @@
         <v>181</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>278</v>
+        <v>223</v>
       </c>
       <c r="C466" s="6">
-        <v>36.950000000000003</v>
+        <v>125</v>
       </c>
       <c r="D466" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -7985,13 +7997,13 @@
         <v>181</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="C467" s="6">
-        <v>39.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D467" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -7999,13 +8011,13 @@
         <v>181</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>8</v>
+        <v>280</v>
       </c>
       <c r="C468" s="6">
-        <v>19.5</v>
+        <v>7.95</v>
       </c>
       <c r="D468" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -8013,13 +8025,13 @@
         <v>181</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="C469" s="6">
-        <v>110</v>
+        <v>18.95</v>
       </c>
       <c r="D469" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -8027,13 +8039,13 @@
         <v>181</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="C470" s="6">
-        <v>98.45</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D470" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -8041,13 +8053,13 @@
         <v>181</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>323</v>
+        <v>127</v>
       </c>
       <c r="C471" s="6">
-        <v>139</v>
+        <v>39.99</v>
       </c>
       <c r="D471" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -8055,10 +8067,10 @@
         <v>181</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>324</v>
+        <v>8</v>
       </c>
       <c r="C472" s="6">
-        <v>199</v>
+        <v>19.5</v>
       </c>
       <c r="D472" t="s">
         <v>139</v>
@@ -8069,10 +8081,10 @@
         <v>181</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C473" s="6">
-        <v>169.99</v>
+        <v>110</v>
       </c>
       <c r="D473" t="s">
         <v>139</v>
@@ -8083,10 +8095,10 @@
         <v>181</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C474" s="6">
-        <v>239.08</v>
+        <v>98.45</v>
       </c>
       <c r="D474" t="s">
         <v>139</v>
@@ -8097,10 +8109,10 @@
         <v>181</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C475" s="6">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="D475" t="s">
         <v>139</v>
@@ -8111,10 +8123,10 @@
         <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C476" s="6">
-        <v>189.99</v>
+        <v>199</v>
       </c>
       <c r="D476" t="s">
         <v>139</v>
@@ -8125,10 +8137,10 @@
         <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C477" s="6">
-        <v>248</v>
+        <v>169.99</v>
       </c>
       <c r="D477" t="s">
         <v>139</v>
@@ -8139,10 +8151,10 @@
         <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C478" s="6">
-        <v>297</v>
+        <v>239.08</v>
       </c>
       <c r="D478" t="s">
         <v>139</v>
@@ -8153,167 +8165,167 @@
         <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C479" s="6">
-        <v>322</v>
+        <v>219</v>
       </c>
       <c r="D479" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
-        <v>224</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C489" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D489" t="s">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>181</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C480" s="6">
+        <v>189.99</v>
+      </c>
+      <c r="D480" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
-        <v>224</v>
-      </c>
-      <c r="B490" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C490" s="6">
-        <v>79.47</v>
-      </c>
-      <c r="D490" t="s">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>181</v>
+      </c>
+      <c r="B481" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C481" s="6">
+        <v>248</v>
+      </c>
+      <c r="D481" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
-        <v>224</v>
-      </c>
-      <c r="B491" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C491" s="6">
-        <v>92.85</v>
-      </c>
-      <c r="D491" t="s">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>181</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C482" s="6">
+        <v>297</v>
+      </c>
+      <c r="D482" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
-        <v>224</v>
-      </c>
-      <c r="B492" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C492" s="6">
-        <v>15.25</v>
-      </c>
-      <c r="D492" t="s">
-        <v>148</v>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>181</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C483" s="6">
+        <v>322</v>
+      </c>
+      <c r="D483" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>224</v>
       </c>
-      <c r="B493" s="3">
-        <v>4442</v>
+      <c r="B493" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="C493" s="6">
-        <v>18.899999999999999</v>
+        <v>42.75</v>
       </c>
       <c r="D493" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>224</v>
       </c>
-      <c r="B494" s="3">
-        <v>6642</v>
+      <c r="B494" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="C494" s="6">
-        <v>26.8</v>
+        <v>79.47</v>
       </c>
       <c r="D494" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>224</v>
       </c>
-      <c r="B495" s="3">
-        <v>6660</v>
+      <c r="B495" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C495" s="6">
-        <v>27.05</v>
+        <v>92.85</v>
       </c>
       <c r="D495" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>224</v>
+      </c>
+      <c r="B496" s="3">
+        <v>4430</v>
+      </c>
+      <c r="C496" s="6">
+        <v>15.25</v>
+      </c>
+      <c r="D496" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>224</v>
+      </c>
+      <c r="B497" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C497" s="6">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D497" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>228</v>
-      </c>
-      <c r="B498" s="3" t="s">
-        <v>9</v>
+        <v>224</v>
+      </c>
+      <c r="B498" s="3">
+        <v>6642</v>
       </c>
       <c r="C498" s="6">
-        <v>47.95</v>
+        <v>26.8</v>
       </c>
       <c r="D498" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>228</v>
-      </c>
-      <c r="B499" s="3" t="s">
-        <v>10</v>
+        <v>224</v>
+      </c>
+      <c r="B499" s="3">
+        <v>6660</v>
       </c>
       <c r="C499" s="6">
-        <v>59.07</v>
+        <v>27.05</v>
       </c>
       <c r="D499" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>228</v>
-      </c>
-      <c r="B500" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C500" s="6">
-        <v>83.8</v>
-      </c>
-      <c r="D500" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>228</v>
-      </c>
-      <c r="B501" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C501" s="6">
-        <v>115.4</v>
-      </c>
-      <c r="D501" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
@@ -8321,10 +8333,10 @@
         <v>228</v>
       </c>
       <c r="B502" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C502" s="6">
-        <v>107.15</v>
+        <v>47.95</v>
       </c>
       <c r="D502" t="s">
         <v>139</v>
@@ -8335,13 +8347,13 @@
         <v>228</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C503" s="6">
-        <v>13</v>
+        <v>59.07</v>
       </c>
       <c r="D503" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -8349,13 +8361,13 @@
         <v>228</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C504" s="6">
-        <v>17</v>
+        <v>83.8</v>
       </c>
       <c r="D504" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -8363,55 +8375,55 @@
         <v>228</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C505" s="6">
-        <v>30</v>
+        <v>115.4</v>
       </c>
       <c r="D505" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>228</v>
       </c>
-      <c r="B506" s="3">
-        <v>4430</v>
+      <c r="B506" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C506" s="6">
-        <v>15.25</v>
+        <v>107.15</v>
       </c>
       <c r="D506" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>228</v>
       </c>
-      <c r="B507" s="3">
-        <v>4442</v>
+      <c r="B507" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C507" s="6">
-        <v>18.899999999999999</v>
+        <v>13</v>
       </c>
       <c r="D507" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>228</v>
       </c>
-      <c r="B508" s="3">
-        <v>6642</v>
+      <c r="B508" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C508" s="6">
-        <v>26.8</v>
+        <v>17</v>
       </c>
       <c r="D508" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
@@ -8419,69 +8431,69 @@
         <v>228</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="C509" s="6">
-        <v>39.950000000000003</v>
+        <v>30</v>
       </c>
       <c r="D509" t="s">
-        <v>150</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>228</v>
+      </c>
+      <c r="B510" s="3">
+        <v>4430</v>
+      </c>
+      <c r="C510" s="6">
+        <v>15.25</v>
+      </c>
+      <c r="D510" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>228</v>
+      </c>
+      <c r="B511" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C511" s="6">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D511" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>229</v>
-      </c>
-      <c r="B512" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
+      </c>
+      <c r="B512" s="3">
+        <v>6642</v>
       </c>
       <c r="C512" s="6">
-        <v>9.92</v>
+        <v>26.8</v>
       </c>
       <c r="D512" t="s">
-        <v>231</v>
+        <v>148</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="C513" s="6">
-        <v>47.95</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="D513" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A514" t="s">
-        <v>229</v>
-      </c>
-      <c r="B514" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C514" s="6">
-        <v>55.73</v>
-      </c>
-      <c r="D514" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A515" t="s">
-        <v>229</v>
-      </c>
-      <c r="B515" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C515" s="6">
-        <v>79.06</v>
-      </c>
-      <c r="D515" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
@@ -8489,13 +8501,13 @@
         <v>229</v>
       </c>
       <c r="B516" s="3" t="s">
-        <v>12</v>
+        <v>230</v>
       </c>
       <c r="C516" s="6">
-        <v>108.86</v>
+        <v>9.92</v>
       </c>
       <c r="D516" t="s">
-        <v>139</v>
+        <v>231</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
@@ -8503,10 +8515,10 @@
         <v>229</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C517" s="6">
-        <v>101.09</v>
+        <v>47.95</v>
       </c>
       <c r="D517" t="s">
         <v>139</v>
@@ -8517,10 +8529,10 @@
         <v>229</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C518" s="6">
-        <v>160.69999999999999</v>
+        <v>55.73</v>
       </c>
       <c r="D518" t="s">
         <v>139</v>
@@ -8531,10 +8543,10 @@
         <v>229</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C519" s="6">
-        <v>121.82</v>
+        <v>79.06</v>
       </c>
       <c r="D519" t="s">
         <v>139</v>
@@ -8545,10 +8557,10 @@
         <v>229</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C520" s="6">
-        <v>122.49</v>
+        <v>108.86</v>
       </c>
       <c r="D520" t="s">
         <v>139</v>
@@ -8559,7 +8571,10 @@
         <v>229</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="C521" s="6">
+        <v>101.09</v>
       </c>
       <c r="D521" t="s">
         <v>139</v>
@@ -8570,7 +8585,10 @@
         <v>229</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="C522" s="6">
+        <v>160.69999999999999</v>
       </c>
       <c r="D522" t="s">
         <v>139</v>
@@ -8581,7 +8599,10 @@
         <v>229</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="C523" s="6">
+        <v>121.82</v>
       </c>
       <c r="D523" t="s">
         <v>139</v>
@@ -8592,10 +8613,10 @@
         <v>229</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="C524" s="6">
-        <v>44</v>
+        <v>122.49</v>
       </c>
       <c r="D524" t="s">
         <v>139</v>
@@ -8606,10 +8627,7 @@
         <v>229</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C525" s="6">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="D525" t="s">
         <v>139</v>
@@ -8620,10 +8638,7 @@
         <v>229</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C526" s="6">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D526" t="s">
         <v>139</v>
@@ -8634,35 +8649,38 @@
         <v>229</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D527" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>229</v>
       </c>
-      <c r="B528" s="3">
-        <v>4430</v>
+      <c r="B528" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C528" s="6">
+        <v>44</v>
       </c>
       <c r="D528" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>229</v>
       </c>
-      <c r="B529" s="3">
-        <v>4442</v>
+      <c r="B529" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="C529" s="6">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D529" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
@@ -8670,13 +8688,13 @@
         <v>229</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>96</v>
+        <v>227</v>
       </c>
       <c r="C530" s="6">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="D530" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
@@ -8684,7 +8702,7 @@
         <v>229</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D531" t="s">
         <v>148</v>
@@ -8695,10 +8713,7 @@
         <v>229</v>
       </c>
       <c r="B532" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C532" s="6">
-        <v>16.5</v>
+        <v>4430</v>
       </c>
       <c r="D532" t="s">
         <v>148</v>
@@ -8708,11 +8723,11 @@
       <c r="A533" t="s">
         <v>229</v>
       </c>
-      <c r="B533" s="3" t="s">
-        <v>98</v>
+      <c r="B533" s="3">
+        <v>4442</v>
       </c>
       <c r="C533" s="6">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="D533" t="s">
         <v>148</v>
@@ -8722,11 +8737,11 @@
       <c r="A534" t="s">
         <v>229</v>
       </c>
-      <c r="B534" s="3">
-        <v>4660</v>
+      <c r="B534" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C534" s="6">
-        <v>20.25</v>
+        <v>171</v>
       </c>
       <c r="D534" t="s">
         <v>148</v>
@@ -8736,8 +8751,8 @@
       <c r="A535" t="s">
         <v>229</v>
       </c>
-      <c r="B535" s="3">
-        <v>6630</v>
+      <c r="B535" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D535" t="s">
         <v>148</v>
@@ -8748,10 +8763,10 @@
         <v>229</v>
       </c>
       <c r="B536" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C536" s="6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="D536" t="s">
         <v>148</v>
@@ -8762,10 +8777,10 @@
         <v>229</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C537" s="6">
-        <v>103.5</v>
+        <v>126</v>
       </c>
       <c r="D537" t="s">
         <v>148</v>
@@ -8776,10 +8791,10 @@
         <v>229</v>
       </c>
       <c r="B538" s="3">
-        <v>6660</v>
+        <v>4660</v>
       </c>
       <c r="C538" s="6">
-        <v>22.5</v>
+        <v>20.25</v>
       </c>
       <c r="D538" t="s">
         <v>148</v>
@@ -8789,11 +8804,8 @@
       <c r="A539" t="s">
         <v>229</v>
       </c>
-      <c r="B539" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C539" s="6">
-        <v>126</v>
+      <c r="B539" s="3">
+        <v>6630</v>
       </c>
       <c r="D539" t="s">
         <v>148</v>
@@ -8804,18 +8816,52 @@
         <v>229</v>
       </c>
       <c r="B540" s="3">
-        <v>8860</v>
+        <v>6642</v>
+      </c>
+      <c r="C540" s="6">
+        <v>18.5</v>
       </c>
       <c r="D540" t="s">
         <v>148</v>
       </c>
     </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>229</v>
+      </c>
+      <c r="B541" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C541" s="6">
+        <v>103.5</v>
+      </c>
+      <c r="D541" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>229</v>
+      </c>
+      <c r="B542" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C542" s="6">
+        <v>22.5</v>
+      </c>
+      <c r="D542" t="s">
+        <v>148</v>
+      </c>
+    </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>233</v>
+        <v>100</v>
+      </c>
+      <c r="C543" s="6">
+        <v>126</v>
       </c>
       <c r="D543" t="s">
         <v>148</v>
@@ -8823,43 +8869,12 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B544" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C544" s="6">
-        <v>15.25</v>
+        <v>8860</v>
       </c>
       <c r="D544" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A545" t="s">
-        <v>232</v>
-      </c>
-      <c r="B545" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C545" s="6">
-        <v>15</v>
-      </c>
-      <c r="D545" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A546" t="s">
-        <v>232</v>
-      </c>
-      <c r="B546" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C546" s="6">
-        <v>171</v>
-      </c>
-      <c r="D546" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8868,10 +8883,7 @@
         <v>232</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C547" s="6">
-        <v>972</v>
+        <v>233</v>
       </c>
       <c r="D547" t="s">
         <v>148</v>
@@ -8882,10 +8894,10 @@
         <v>232</v>
       </c>
       <c r="B548" s="3">
-        <v>4642</v>
+        <v>4430</v>
       </c>
       <c r="C548" s="6">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
       <c r="D548" t="s">
         <v>148</v>
@@ -8895,11 +8907,11 @@
       <c r="A549" t="s">
         <v>232</v>
       </c>
-      <c r="B549" s="3" t="s">
-        <v>98</v>
+      <c r="B549" s="3">
+        <v>4442</v>
       </c>
       <c r="C549" s="6">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="D549" t="s">
         <v>148</v>
@@ -8909,11 +8921,11 @@
       <c r="A550" t="s">
         <v>232</v>
       </c>
-      <c r="B550" s="3">
-        <v>4660</v>
+      <c r="B550" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C550" s="6">
-        <v>20.25</v>
+        <v>171</v>
       </c>
       <c r="D550" t="s">
         <v>148</v>
@@ -8923,11 +8935,11 @@
       <c r="A551" t="s">
         <v>232</v>
       </c>
-      <c r="B551" s="3">
-        <v>6630</v>
+      <c r="B551" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="C551" s="6">
-        <v>19</v>
+        <v>972</v>
       </c>
       <c r="D551" t="s">
         <v>148</v>
@@ -8938,10 +8950,10 @@
         <v>232</v>
       </c>
       <c r="B552" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C552" s="6">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="D552" t="s">
         <v>148</v>
@@ -8952,10 +8964,10 @@
         <v>232</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C553" s="6">
-        <v>103.5</v>
+        <v>126</v>
       </c>
       <c r="D553" t="s">
         <v>148</v>
@@ -8966,10 +8978,10 @@
         <v>232</v>
       </c>
       <c r="B554" s="3">
-        <v>6660</v>
+        <v>4660</v>
       </c>
       <c r="C554" s="6">
-        <v>22.5</v>
+        <v>20.25</v>
       </c>
       <c r="D554" t="s">
         <v>148</v>
@@ -8979,11 +8991,11 @@
       <c r="A555" t="s">
         <v>232</v>
       </c>
-      <c r="B555" s="3" t="s">
-        <v>100</v>
+      <c r="B555" s="3">
+        <v>6630</v>
       </c>
       <c r="C555" s="6">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="D555" t="s">
         <v>148</v>
@@ -8994,10 +9006,10 @@
         <v>232</v>
       </c>
       <c r="B556" s="3">
-        <v>8860</v>
+        <v>6642</v>
       </c>
       <c r="C556" s="6">
-        <v>42.25</v>
+        <v>18.5</v>
       </c>
       <c r="D556" t="s">
         <v>148</v>
@@ -9008,27 +9020,27 @@
         <v>232</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>316</v>
+        <v>99</v>
       </c>
       <c r="C557" s="6">
-        <v>5.75</v>
+        <v>103.5</v>
       </c>
       <c r="D557" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>232</v>
       </c>
-      <c r="B558" s="3" t="s">
-        <v>317</v>
+      <c r="B558" s="3">
+        <v>6660</v>
       </c>
       <c r="C558" s="6">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D558" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
@@ -9036,27 +9048,27 @@
         <v>232</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>318</v>
+        <v>100</v>
       </c>
       <c r="C559" s="6">
-        <v>12.5</v>
+        <v>126</v>
       </c>
       <c r="D559" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>232</v>
       </c>
-      <c r="B560" s="3" t="s">
-        <v>306</v>
+      <c r="B560" s="3">
+        <v>8860</v>
       </c>
       <c r="C560" s="6">
-        <v>77.5</v>
+        <v>42.25</v>
       </c>
       <c r="D560" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
@@ -9064,69 +9076,69 @@
         <v>232</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C561" s="6">
-        <v>195</v>
+        <v>5.75</v>
       </c>
       <c r="D561" t="s">
         <v>309</v>
       </c>
     </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>232</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C562" s="6">
+        <v>20</v>
+      </c>
+      <c r="D562" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>232</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C563" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="D563" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>232</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C564" s="6">
+        <v>77.5</v>
+      </c>
+      <c r="D564" t="s">
+        <v>309</v>
+      </c>
+    </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>9</v>
+        <v>307</v>
       </c>
       <c r="C565" s="6">
-        <v>50.35</v>
+        <v>195</v>
       </c>
       <c r="D565" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A566" t="s">
-        <v>276</v>
-      </c>
-      <c r="B566" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C566" s="6">
-        <v>41.99</v>
-      </c>
-      <c r="D566" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A567" t="s">
-        <v>276</v>
-      </c>
-      <c r="B567" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C567" s="6">
-        <v>82</v>
-      </c>
-      <c r="D567" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A568" t="s">
-        <v>276</v>
-      </c>
-      <c r="B568" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C568" s="6">
-        <v>28</v>
-      </c>
-      <c r="D568" t="s">
-        <v>145</v>
+        <v>309</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
@@ -9134,13 +9146,13 @@
         <v>276</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="C569" s="6">
-        <v>28.05</v>
+        <v>50.35</v>
       </c>
       <c r="D569" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
@@ -9148,13 +9160,13 @@
         <v>276</v>
       </c>
       <c r="B570" s="3" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C570" s="6">
-        <v>28.05</v>
+        <v>41.99</v>
       </c>
       <c r="D570" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
@@ -9162,13 +9174,13 @@
         <v>276</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="C571" s="6">
-        <v>28.05</v>
+        <v>82</v>
       </c>
       <c r="D571" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
@@ -9176,69 +9188,69 @@
         <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>117</v>
+        <v>256</v>
       </c>
       <c r="C572" s="6">
-        <v>11.2</v>
+        <v>28</v>
       </c>
       <c r="D572" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>276</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C573" s="6">
+        <v>28.05</v>
+      </c>
+      <c r="D573" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>276</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C574" s="6">
+        <v>28.05</v>
+      </c>
+      <c r="D574" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>144</v>
+        <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C575" s="6">
-        <v>29.87</v>
+        <v>28.05</v>
       </c>
       <c r="D575" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>144</v>
+        <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C576" s="6">
-        <v>199</v>
+        <v>11.2</v>
       </c>
       <c r="D576" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A577" t="s">
-        <v>144</v>
-      </c>
-      <c r="B577" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C577" s="6">
-        <v>175</v>
-      </c>
-      <c r="D577" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A578" t="s">
-        <v>144</v>
-      </c>
-      <c r="B578" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C578" s="6">
-        <v>189</v>
-      </c>
-      <c r="D578" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.25">
@@ -9246,13 +9258,13 @@
         <v>144</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C579" s="6">
-        <v>309</v>
+        <v>29.87</v>
       </c>
       <c r="D579" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.25">
@@ -9260,13 +9272,13 @@
         <v>144</v>
       </c>
       <c r="B580" s="3" t="s">
-        <v>212</v>
+        <v>16</v>
       </c>
       <c r="C580" s="6">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="D580" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
@@ -9274,13 +9286,13 @@
         <v>144</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>202</v>
+        <v>28</v>
       </c>
       <c r="C581" s="6">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D581" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
@@ -9288,13 +9300,13 @@
         <v>144</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C582" s="6">
-        <v>59.99</v>
+        <v>189</v>
       </c>
       <c r="D582" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9302,13 +9314,13 @@
         <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>256</v>
+        <v>31</v>
       </c>
       <c r="C583" s="6">
-        <v>32.99</v>
+        <v>309</v>
       </c>
       <c r="D583" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -9316,13 +9328,13 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>58</v>
+        <v>212</v>
       </c>
       <c r="C584" s="6">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="D584" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
@@ -9330,13 +9342,13 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="C585" s="6">
-        <v>149.99</v>
+        <v>134</v>
       </c>
       <c r="D585" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
@@ -9344,13 +9356,13 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C586" s="6">
-        <v>47.99</v>
+        <v>59.99</v>
       </c>
       <c r="D586" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
@@ -9358,13 +9370,13 @@
         <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="C587" s="6">
-        <v>39.99</v>
+        <v>32.99</v>
       </c>
       <c r="D587" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
@@ -9372,13 +9384,13 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="C588" s="6">
-        <v>39.99</v>
+        <v>129</v>
       </c>
       <c r="D588" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.25">
@@ -9386,10 +9398,13 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>106</v>
+        <v>257</v>
+      </c>
+      <c r="C589" s="6">
+        <v>149.99</v>
       </c>
       <c r="D589" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.25">
@@ -9397,69 +9412,66 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>278</v>
+        <v>59</v>
       </c>
       <c r="C590" s="6">
-        <v>36.950000000000003</v>
+        <v>47.99</v>
       </c>
       <c r="D590" t="s">
-        <v>173</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>144</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C591" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D591" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>144</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C592" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D592" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C593" s="6">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="D593" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
-        <v>9</v>
+        <v>278</v>
       </c>
       <c r="C594" s="6">
-        <v>100</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D594" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A595" t="s">
-        <v>288</v>
-      </c>
-      <c r="B595" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C595" s="6">
-        <v>99</v>
-      </c>
-      <c r="D595" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A596" t="s">
-        <v>288</v>
-      </c>
-      <c r="B596" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C596" s="6">
-        <v>134</v>
-      </c>
-      <c r="D596" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.25">
@@ -9467,10 +9479,10 @@
         <v>288</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C597" s="6">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="D597" t="s">
         <v>139</v>
@@ -9481,10 +9493,10 @@
         <v>288</v>
       </c>
       <c r="B598" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C598" s="6">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="D598" t="s">
         <v>139</v>
@@ -9495,10 +9507,10 @@
         <v>288</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C599" s="6">
-        <v>239</v>
+        <v>99</v>
       </c>
       <c r="D599" t="s">
         <v>139</v>
@@ -9509,10 +9521,10 @@
         <v>288</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C600" s="6">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="D600" t="s">
         <v>139</v>
@@ -9523,10 +9535,10 @@
         <v>288</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C601" s="6">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D601" t="s">
         <v>139</v>
@@ -9537,10 +9549,10 @@
         <v>288</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C602" s="6">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="D602" t="s">
         <v>139</v>
@@ -9551,10 +9563,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C603" s="6">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9565,10 +9577,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C604" s="6">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9579,13 +9591,13 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C605" s="6">
-        <v>19.989999999999998</v>
+        <v>189</v>
       </c>
       <c r="D605" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
@@ -9593,13 +9605,13 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C606" s="6">
-        <v>29.99</v>
+        <v>210</v>
       </c>
       <c r="D606" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
@@ -9607,13 +9619,13 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C607" s="6">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="D607" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
@@ -9621,13 +9633,13 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C608" s="6">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="D608" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
@@ -9635,13 +9647,13 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C609" s="6">
-        <v>180</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D609" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
@@ -9649,13 +9661,13 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C610" s="6">
-        <v>170</v>
+        <v>29.99</v>
       </c>
       <c r="D610" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
@@ -9663,10 +9675,10 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C611" s="6">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="D611" t="s">
         <v>142</v>
@@ -9677,10 +9689,10 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C612" s="6">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="D612" t="s">
         <v>142</v>
@@ -9691,10 +9703,10 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C613" s="6">
-        <v>399.99</v>
+        <v>180</v>
       </c>
       <c r="D613" t="s">
         <v>142</v>
@@ -9705,10 +9717,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C614" s="6">
-        <v>89.23</v>
+        <v>170</v>
       </c>
       <c r="D614" t="s">
         <v>142</v>
@@ -9718,14 +9730,14 @@
       <c r="A615" t="s">
         <v>288</v>
       </c>
-      <c r="B615" s="3">
-        <v>6102</v>
+      <c r="B615" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C615" s="6">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="D615" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
@@ -9733,13 +9745,13 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>281</v>
+        <v>31</v>
       </c>
       <c r="C616" s="6">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="D616" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
@@ -9747,13 +9759,13 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="C617" s="6">
-        <v>69</v>
+        <v>399.99</v>
       </c>
       <c r="D617" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.25">
@@ -9761,27 +9773,27 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>283</v>
+        <v>37</v>
       </c>
       <c r="C618" s="6">
-        <v>72</v>
+        <v>89.23</v>
       </c>
       <c r="D618" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>288</v>
       </c>
-      <c r="B619" s="3" t="s">
-        <v>284</v>
+      <c r="B619" s="3">
+        <v>6102</v>
       </c>
       <c r="C619" s="6">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D619" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
@@ -9789,10 +9801,10 @@
         <v>288</v>
       </c>
       <c r="B620" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C620" s="6">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D620" t="s">
         <v>269</v>
@@ -9803,10 +9815,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C621" s="6">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="D621" t="s">
         <v>269</v>
@@ -9817,13 +9829,13 @@
         <v>288</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>55</v>
+        <v>283</v>
       </c>
       <c r="C622" s="6">
-        <v>27.99</v>
+        <v>72</v>
       </c>
       <c r="D622" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
@@ -9831,13 +9843,13 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="C623" s="6">
-        <v>28.99</v>
+        <v>77</v>
       </c>
       <c r="D623" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.25">
@@ -9845,13 +9857,13 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>56</v>
+        <v>285</v>
       </c>
       <c r="C624" s="6">
-        <v>39.99</v>
+        <v>90</v>
       </c>
       <c r="D624" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.25">
@@ -9859,13 +9871,13 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>57</v>
+        <v>286</v>
       </c>
       <c r="C625" s="6">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="D625" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.25">
@@ -9873,10 +9885,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>256</v>
+        <v>55</v>
       </c>
       <c r="C626" s="6">
-        <v>42.99</v>
+        <v>27.99</v>
       </c>
       <c r="D626" t="s">
         <v>145</v>
@@ -9887,10 +9899,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>58</v>
+        <v>255</v>
       </c>
       <c r="C627" s="6">
-        <v>129</v>
+        <v>28.99</v>
       </c>
       <c r="D627" t="s">
         <v>145</v>
@@ -9901,10 +9913,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>257</v>
+        <v>56</v>
       </c>
       <c r="C628" s="6">
-        <v>180</v>
+        <v>39.99</v>
       </c>
       <c r="D628" t="s">
         <v>145</v>
@@ -9915,13 +9927,13 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C629" s="6">
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="D629" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.25">
@@ -9929,13 +9941,13 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="C630" s="6">
-        <v>48.99</v>
+        <v>42.99</v>
       </c>
       <c r="D630" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.25">
@@ -9943,13 +9955,13 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C631" s="6">
-        <v>39.99</v>
+        <v>129</v>
       </c>
       <c r="D631" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.25">
@@ -9957,13 +9969,13 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="C632" s="6">
-        <v>64.989999999999995</v>
+        <v>180</v>
       </c>
       <c r="D632" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.25">
@@ -9971,10 +9983,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C633" s="6">
-        <v>29.99</v>
+        <v>54.5</v>
       </c>
       <c r="D633" t="s">
         <v>146</v>
@@ -9985,10 +9997,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C634" s="6">
-        <v>28.99</v>
+        <v>48.99</v>
       </c>
       <c r="D634" t="s">
         <v>146</v>
@@ -9999,7 +10011,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>176</v>
+        <v>63</v>
+      </c>
+      <c r="C635" s="6">
+        <v>39.99</v>
       </c>
       <c r="D635" t="s">
         <v>146</v>
@@ -10010,10 +10025,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C636" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D636" t="s">
         <v>146</v>
@@ -10024,10 +10039,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C637" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D637" t="s">
         <v>146</v>
@@ -10037,14 +10052,14 @@
       <c r="A638" t="s">
         <v>288</v>
       </c>
-      <c r="B638" s="3">
-        <v>6642</v>
+      <c r="B638" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C638" s="6">
-        <v>50</v>
+        <v>28.99</v>
       </c>
       <c r="D638" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.25">
@@ -10052,13 +10067,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C639" s="6">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="D639" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.25">
@@ -10066,13 +10078,13 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="C640" s="6">
-        <v>40</v>
+        <v>29.99</v>
       </c>
       <c r="D640" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.25">
@@ -10080,122 +10092,125 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="C641" s="6">
-        <v>39.99</v>
+        <v>25.99</v>
       </c>
       <c r="D641" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>288</v>
       </c>
-      <c r="B642" s="3" t="s">
-        <v>287</v>
+      <c r="B642" s="3">
+        <v>6642</v>
       </c>
       <c r="C642" s="6">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D642" t="s">
-        <v>154</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A643" t="s">
+        <v>288</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C643" s="6">
+        <v>40</v>
+      </c>
+      <c r="D643" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A644" t="s">
+        <v>288</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C644" s="6">
+        <v>40</v>
+      </c>
+      <c r="D644" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="C645" s="6">
-        <v>42.75</v>
+        <v>39.99</v>
       </c>
       <c r="D645" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="C646" s="6">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D646" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A647" t="s">
-        <v>290</v>
-      </c>
-      <c r="B647" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C647" s="6">
-        <v>82.2</v>
-      </c>
-      <c r="D647" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="C649" s="6">
-        <v>10</v>
+        <v>42.75</v>
       </c>
       <c r="D649" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>23</v>
+        <v>226</v>
+      </c>
+      <c r="C650" s="6">
+        <v>68</v>
       </c>
       <c r="D650" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>304</v>
-      </c>
-      <c r="B651" s="3">
-        <v>4642</v>
+        <v>290</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C651" s="6">
-        <v>18.96</v>
+        <v>82.2</v>
       </c>
       <c r="D651" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A652" t="s">
-        <v>304</v>
-      </c>
-      <c r="B652" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C652" s="6">
-        <v>22.37</v>
-      </c>
-      <c r="D652" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.25">
@@ -10203,13 +10218,13 @@
         <v>304</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="C653" s="6">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="D653" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
@@ -10217,97 +10232,94 @@
         <v>304</v>
       </c>
       <c r="B654" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D654" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A655" t="s">
+        <v>304</v>
+      </c>
+      <c r="B655" s="3">
+        <v>4642</v>
+      </c>
+      <c r="C655" s="6">
+        <v>18.96</v>
+      </c>
+      <c r="D655" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A656" t="s">
+        <v>304</v>
+      </c>
+      <c r="B656" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C656" s="6">
+        <v>22.37</v>
+      </c>
+      <c r="D656" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A657" t="s">
+        <v>304</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C657" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D657" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A658" t="s">
+        <v>304</v>
+      </c>
+      <c r="B658" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C654" s="6">
+      <c r="C658" s="6">
         <v>9.1</v>
       </c>
-      <c r="D654" t="s">
+      <c r="D658" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A659" t="s">
+    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A663" t="s">
         <v>292</v>
       </c>
-      <c r="B659" s="3" t="s">
+      <c r="B663" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C659" s="6">
+      <c r="C663" s="6">
         <v>5</v>
       </c>
-      <c r="D659" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A660" t="s">
-        <v>292</v>
-      </c>
-      <c r="B660" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C660" s="6">
-        <v>5</v>
-      </c>
-      <c r="D660" t="s">
+      <c r="D663" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="C664" s="6">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="D664" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A665" t="s">
-        <v>293</v>
-      </c>
-      <c r="B665" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C665" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="D665" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A666" t="s">
-        <v>293</v>
-      </c>
-      <c r="B666" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C666" s="6">
-        <v>8.1</v>
-      </c>
-      <c r="D666" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A667" t="s">
-        <v>293</v>
-      </c>
-      <c r="B667" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C667" s="6">
-        <v>10.8</v>
-      </c>
-      <c r="D667" t="s">
-        <v>303</v>
+        <v>140</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.25">
@@ -10315,10 +10327,10 @@
         <v>293</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C668" s="6">
-        <v>12.2</v>
+        <v>3.15</v>
       </c>
       <c r="D668" t="s">
         <v>303</v>
@@ -10329,10 +10341,10 @@
         <v>293</v>
       </c>
       <c r="B669" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C669" s="6">
-        <v>11.25</v>
+        <v>7.65</v>
       </c>
       <c r="D669" t="s">
         <v>303</v>
@@ -10343,10 +10355,10 @@
         <v>293</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C670" s="6">
-        <v>11.25</v>
+        <v>8.1</v>
       </c>
       <c r="D670" t="s">
         <v>303</v>
@@ -10357,24 +10369,52 @@
         <v>293</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C671" s="6">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="D671" t="s">
         <v>303</v>
       </c>
     </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A672" t="s">
+        <v>293</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C672" s="6">
+        <v>12.2</v>
+      </c>
+      <c r="D672" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A673" t="s">
+        <v>293</v>
+      </c>
+      <c r="B673" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C673" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D673" t="s">
+        <v>303</v>
+      </c>
+    </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C674" s="6">
-        <v>3.36</v>
+        <v>11.25</v>
       </c>
       <c r="D674" t="s">
         <v>303</v>
@@ -10382,43 +10422,15 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C675" s="6">
-        <v>10.19</v>
+        <v>11.25</v>
       </c>
       <c r="D675" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A676" t="s">
-        <v>294</v>
-      </c>
-      <c r="B676" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C676" s="6">
-        <v>14.4</v>
-      </c>
-      <c r="D676" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A677" t="s">
-        <v>294</v>
-      </c>
-      <c r="B677" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C677" s="6">
-        <v>14.39</v>
-      </c>
-      <c r="D677" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10427,10 +10439,10 @@
         <v>294</v>
       </c>
       <c r="B678" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C678" s="6">
-        <v>11.52</v>
+        <v>3.36</v>
       </c>
       <c r="D678" t="s">
         <v>303</v>
@@ -10441,10 +10453,10 @@
         <v>294</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C679" s="6">
-        <v>12</v>
+        <v>10.19</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10455,10 +10467,10 @@
         <v>294</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C680" s="6">
-        <v>12</v>
+        <v>14.4</v>
       </c>
       <c r="D680" t="s">
         <v>303</v>
@@ -10469,12 +10481,68 @@
         <v>294</v>
       </c>
       <c r="B681" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C681" s="6">
+        <v>14.39</v>
+      </c>
+      <c r="D681" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A682" t="s">
+        <v>294</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C682" s="6">
+        <v>11.52</v>
+      </c>
+      <c r="D682" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A683" t="s">
+        <v>294</v>
+      </c>
+      <c r="B683" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C683" s="6">
+        <v>12</v>
+      </c>
+      <c r="D683" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A684" t="s">
+        <v>294</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C684" s="6">
+        <v>12</v>
+      </c>
+      <c r="D684" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A685" t="s">
+        <v>294</v>
+      </c>
+      <c r="B685" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C681" s="6">
+      <c r="C685" s="6">
         <v>12</v>
       </c>
-      <c r="D681" t="s">
+      <c r="D685" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B11EBB-97A9-4C91-9AB0-4110DCD85C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94EACF6-E4F4-4909-B1E8-D98F855677B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="337">
   <si>
     <t>BGC10</t>
   </si>
@@ -1433,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K685"/>
+  <dimension ref="A1:K686"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -9759,10 +9759,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C617" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9773,10 +9773,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C618" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9786,28 +9786,28 @@
       <c r="A619" t="s">
         <v>288</v>
       </c>
-      <c r="B619" s="3">
-        <v>6102</v>
+      <c r="B619" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C619" s="6">
-        <v>44</v>
+        <v>89.23</v>
       </c>
       <c r="D619" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>288</v>
       </c>
-      <c r="B620" s="3" t="s">
-        <v>281</v>
+      <c r="B620" s="3">
+        <v>6102</v>
       </c>
       <c r="C620" s="6">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D620" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
@@ -9815,10 +9815,10 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C621" s="6">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D621" t="s">
         <v>269</v>
@@ -9829,10 +9829,10 @@
         <v>288</v>
       </c>
       <c r="B622" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C622" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D622" t="s">
         <v>269</v>
@@ -9843,10 +9843,10 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C623" s="6">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D623" t="s">
         <v>269</v>
@@ -9857,10 +9857,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C624" s="6">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D624" t="s">
         <v>269</v>
@@ -9871,10 +9871,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C625" s="6">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D625" t="s">
         <v>269</v>
@@ -9885,13 +9885,13 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="C626" s="6">
-        <v>27.99</v>
+        <v>114</v>
       </c>
       <c r="D626" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.25">
@@ -9899,10 +9899,10 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>255</v>
+        <v>55</v>
       </c>
       <c r="C627" s="6">
-        <v>28.99</v>
+        <v>27.99</v>
       </c>
       <c r="D627" t="s">
         <v>145</v>
@@ -9913,10 +9913,10 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C628" s="6">
-        <v>39.99</v>
+        <v>28.99</v>
       </c>
       <c r="D628" t="s">
         <v>145</v>
@@ -9927,10 +9927,10 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C629" s="6">
-        <v>58</v>
+        <v>39.99</v>
       </c>
       <c r="D629" t="s">
         <v>145</v>
@@ -9941,10 +9941,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="C630" s="6">
-        <v>42.99</v>
+        <v>58</v>
       </c>
       <c r="D630" t="s">
         <v>145</v>
@@ -9955,10 +9955,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="C631" s="6">
-        <v>129</v>
+        <v>42.99</v>
       </c>
       <c r="D631" t="s">
         <v>145</v>
@@ -9969,10 +9969,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>257</v>
+        <v>58</v>
       </c>
       <c r="C632" s="6">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D632" t="s">
         <v>145</v>
@@ -9983,13 +9983,13 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>59</v>
+        <v>257</v>
       </c>
       <c r="C633" s="6">
-        <v>54.5</v>
+        <v>180</v>
       </c>
       <c r="D633" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.25">
@@ -9997,10 +9997,10 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C634" s="6">
-        <v>48.99</v>
+        <v>54.5</v>
       </c>
       <c r="D634" t="s">
         <v>146</v>
@@ -10011,10 +10011,10 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C635" s="6">
-        <v>39.99</v>
+        <v>48.99</v>
       </c>
       <c r="D635" t="s">
         <v>146</v>
@@ -10025,10 +10025,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C636" s="6">
-        <v>64.989999999999995</v>
+        <v>39.99</v>
       </c>
       <c r="D636" t="s">
         <v>146</v>
@@ -10039,10 +10039,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C637" s="6">
-        <v>29.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D637" t="s">
         <v>146</v>
@@ -10053,10 +10053,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C638" s="6">
-        <v>28.99</v>
+        <v>29.99</v>
       </c>
       <c r="D638" t="s">
         <v>146</v>
@@ -10067,7 +10067,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>176</v>
+        <v>66</v>
+      </c>
+      <c r="C639" s="6">
+        <v>28.99</v>
       </c>
       <c r="D639" t="s">
         <v>146</v>
@@ -10078,10 +10081,7 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C640" s="6">
-        <v>29.99</v>
+        <v>176</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10092,10 +10092,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C641" s="6">
-        <v>25.99</v>
+        <v>29.99</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10105,28 +10105,28 @@
       <c r="A642" t="s">
         <v>288</v>
       </c>
-      <c r="B642" s="3">
-        <v>6642</v>
+      <c r="B642" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="C642" s="6">
-        <v>50</v>
+        <v>25.99</v>
       </c>
       <c r="D642" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>288</v>
       </c>
-      <c r="B643" s="3" t="s">
-        <v>109</v>
+      <c r="B643" s="3">
+        <v>6642</v>
       </c>
       <c r="C643" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D643" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
@@ -10134,7 +10134,7 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C644" s="6">
         <v>40</v>
@@ -10148,13 +10148,13 @@
         <v>288</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C645" s="6">
-        <v>39.99</v>
+        <v>40</v>
       </c>
       <c r="D645" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
@@ -10162,27 +10162,27 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="C646" s="6">
-        <v>90</v>
+        <v>39.99</v>
       </c>
       <c r="D646" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A649" t="s">
-        <v>290</v>
-      </c>
-      <c r="B649" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C649" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D649" t="s">
-        <v>139</v>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A647" t="s">
+        <v>288</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C647" s="6">
+        <v>90</v>
+      </c>
+      <c r="D647" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.25">
@@ -10190,10 +10190,10 @@
         <v>290</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C650" s="6">
-        <v>68</v>
+        <v>42.75</v>
       </c>
       <c r="D650" t="s">
         <v>139</v>
@@ -10204,27 +10204,27 @@
         <v>290</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C651" s="6">
-        <v>82.2</v>
+        <v>68</v>
       </c>
       <c r="D651" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A653" t="s">
-        <v>304</v>
-      </c>
-      <c r="B653" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C653" s="6">
-        <v>10</v>
-      </c>
-      <c r="D653" t="s">
-        <v>140</v>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A652" t="s">
+        <v>290</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C652" s="6">
+        <v>82.2</v>
+      </c>
+      <c r="D652" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
@@ -10232,7 +10232,10 @@
         <v>304</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="C654" s="6">
+        <v>10</v>
       </c>
       <c r="D654" t="s">
         <v>140</v>
@@ -10242,14 +10245,11 @@
       <c r="A655" t="s">
         <v>304</v>
       </c>
-      <c r="B655" s="3">
-        <v>4642</v>
-      </c>
-      <c r="C655" s="6">
-        <v>18.96</v>
+      <c r="B655" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D655" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
@@ -10257,10 +10257,10 @@
         <v>304</v>
       </c>
       <c r="B656" s="3">
-        <v>6642</v>
+        <v>4642</v>
       </c>
       <c r="C656" s="6">
-        <v>22.37</v>
+        <v>18.96</v>
       </c>
       <c r="D656" t="s">
         <v>148</v>
@@ -10270,14 +10270,14 @@
       <c r="A657" t="s">
         <v>304</v>
       </c>
-      <c r="B657" s="3" t="s">
-        <v>116</v>
+      <c r="B657" s="3">
+        <v>6642</v>
       </c>
       <c r="C657" s="6">
-        <v>9.1</v>
+        <v>22.37</v>
       </c>
       <c r="D657" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
@@ -10285,7 +10285,7 @@
         <v>304</v>
       </c>
       <c r="B658" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C658" s="6">
         <v>9.1</v>
@@ -10294,18 +10294,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A663" t="s">
-        <v>292</v>
-      </c>
-      <c r="B663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C663" s="6">
-        <v>5</v>
-      </c>
-      <c r="D663" t="s">
-        <v>140</v>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A659" t="s">
+        <v>304</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C659" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D659" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>292</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C664" s="6">
         <v>5</v>
@@ -10322,18 +10322,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A668" t="s">
-        <v>293</v>
-      </c>
-      <c r="B668" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C668" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D668" t="s">
-        <v>303</v>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A665" t="s">
+        <v>292</v>
+      </c>
+      <c r="B665" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C665" s="6">
+        <v>5</v>
+      </c>
+      <c r="D665" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.25">
@@ -10341,10 +10341,10 @@
         <v>293</v>
       </c>
       <c r="B669" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C669" s="6">
-        <v>7.65</v>
+        <v>3.15</v>
       </c>
       <c r="D669" t="s">
         <v>303</v>
@@ -10355,10 +10355,10 @@
         <v>293</v>
       </c>
       <c r="B670" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C670" s="6">
-        <v>8.1</v>
+        <v>7.65</v>
       </c>
       <c r="D670" t="s">
         <v>303</v>
@@ -10369,10 +10369,10 @@
         <v>293</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C671" s="6">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="D671" t="s">
         <v>303</v>
@@ -10383,10 +10383,10 @@
         <v>293</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C672" s="6">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
       <c r="D672" t="s">
         <v>303</v>
@@ -10397,10 +10397,10 @@
         <v>293</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C673" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D673" t="s">
         <v>303</v>
@@ -10411,7 +10411,7 @@
         <v>293</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C674" s="6">
         <v>11.25</v>
@@ -10425,7 +10425,7 @@
         <v>293</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C675" s="6">
         <v>11.25</v>
@@ -10434,17 +10434,17 @@
         <v>303</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A678" t="s">
-        <v>294</v>
-      </c>
-      <c r="B678" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C678" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D678" t="s">
+    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A676" t="s">
+        <v>293</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C676" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D676" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10453,10 +10453,10 @@
         <v>294</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C679" s="6">
-        <v>10.19</v>
+        <v>3.36</v>
       </c>
       <c r="D679" t="s">
         <v>303</v>
@@ -10467,10 +10467,10 @@
         <v>294</v>
       </c>
       <c r="B680" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C680" s="6">
-        <v>14.4</v>
+        <v>10.19</v>
       </c>
       <c r="D680" t="s">
         <v>303</v>
@@ -10481,10 +10481,10 @@
         <v>294</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C681" s="6">
-        <v>14.39</v>
+        <v>14.4</v>
       </c>
       <c r="D681" t="s">
         <v>303</v>
@@ -10495,10 +10495,10 @@
         <v>294</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C682" s="6">
-        <v>11.52</v>
+        <v>14.39</v>
       </c>
       <c r="D682" t="s">
         <v>303</v>
@@ -10509,10 +10509,10 @@
         <v>294</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C683" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D683" t="s">
         <v>303</v>
@@ -10523,7 +10523,7 @@
         <v>294</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C684" s="6">
         <v>12</v>
@@ -10537,12 +10537,26 @@
         <v>294</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C685" s="6">
         <v>12</v>
       </c>
       <c r="D685" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A686" t="s">
+        <v>294</v>
+      </c>
+      <c r="B686" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C686" s="6">
+        <v>12</v>
+      </c>
+      <c r="D686" t="s">
         <v>303</v>
       </c>
     </row>

--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94EACF6-E4F4-4909-B1E8-D98F855677B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB0AAA1-4129-47F6-B4B0-EA7473431854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="339">
   <si>
     <t>BGC10</t>
   </si>
@@ -1036,6 +1036,12 @@
   </si>
   <si>
     <t>Habitat PRO-RS-25lbs</t>
+  </si>
+  <si>
+    <t>RS25</t>
+  </si>
+  <si>
+    <t>RS10</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K686"/>
+  <dimension ref="A1:K688"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -6082,13 +6088,10 @@
         <v>175</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C325" s="6">
-        <v>12</v>
+        <v>338</v>
       </c>
       <c r="D325" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -6096,13 +6099,13 @@
         <v>175</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>56</v>
+        <v>337</v>
       </c>
       <c r="C326" s="6">
-        <v>21</v>
+        <v>15.58</v>
       </c>
       <c r="D326" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -6110,10 +6113,10 @@
         <v>175</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C327" s="6">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D327" t="s">
         <v>145</v>
@@ -6124,10 +6127,10 @@
         <v>175</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C328" s="6">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="D328" t="s">
         <v>145</v>
@@ -6137,11 +6140,11 @@
       <c r="A329" t="s">
         <v>175</v>
       </c>
-      <c r="B329" t="s">
-        <v>255</v>
+      <c r="B329" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="C329" s="6">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D329" t="s">
         <v>145</v>
@@ -6151,11 +6154,11 @@
       <c r="A330" t="s">
         <v>175</v>
       </c>
-      <c r="B330" t="s">
-        <v>256</v>
+      <c r="B330" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C330" s="6">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D330" t="s">
         <v>145</v>
@@ -6166,10 +6169,10 @@
         <v>175</v>
       </c>
       <c r="B331" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C331" s="6">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="D331" t="s">
         <v>145</v>
@@ -6179,39 +6182,39 @@
       <c r="A332" t="s">
         <v>175</v>
       </c>
-      <c r="B332" s="3" t="s">
-        <v>59</v>
+      <c r="B332" t="s">
+        <v>256</v>
       </c>
       <c r="C332" s="6">
-        <v>33.5</v>
+        <v>28</v>
       </c>
       <c r="D332" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>175</v>
       </c>
-      <c r="B333" s="3" t="s">
-        <v>60</v>
+      <c r="B333" t="s">
+        <v>257</v>
       </c>
       <c r="C333" s="6">
-        <v>15.1</v>
+        <v>102</v>
       </c>
       <c r="D333" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>175</v>
       </c>
-      <c r="B334" t="s">
-        <v>61</v>
+      <c r="B334" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C334" s="6">
-        <v>38.28</v>
+        <v>33.5</v>
       </c>
       <c r="D334" t="s">
         <v>146</v>
@@ -6222,10 +6225,10 @@
         <v>175</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C335" s="6">
-        <v>22.36</v>
+        <v>15.1</v>
       </c>
       <c r="D335" t="s">
         <v>146</v>
@@ -6235,11 +6238,11 @@
       <c r="A336" t="s">
         <v>175</v>
       </c>
-      <c r="B336" s="3" t="s">
-        <v>176</v>
+      <c r="B336" t="s">
+        <v>61</v>
       </c>
       <c r="C336" s="6">
-        <v>23.68</v>
+        <v>38.28</v>
       </c>
       <c r="D336" t="s">
         <v>146</v>
@@ -6250,10 +6253,10 @@
         <v>175</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C337" s="6">
-        <v>10</v>
+        <v>22.36</v>
       </c>
       <c r="D337" t="s">
         <v>146</v>
@@ -6264,13 +6267,13 @@
         <v>175</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C338" s="6">
-        <v>87</v>
+        <v>23.68</v>
       </c>
       <c r="D338" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -6278,13 +6281,13 @@
         <v>175</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="C339" s="6">
-        <v>225</v>
+        <v>10</v>
       </c>
       <c r="D339" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -6292,10 +6295,10 @@
         <v>175</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C340" s="6">
-        <v>421.08</v>
+        <v>87</v>
       </c>
       <c r="D340" t="s">
         <v>147</v>
@@ -6306,10 +6309,13 @@
         <v>175</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>92</v>
+        <v>178</v>
+      </c>
+      <c r="C341" s="6">
+        <v>225</v>
       </c>
       <c r="D341" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -6317,13 +6323,13 @@
         <v>175</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>93</v>
+        <v>179</v>
       </c>
       <c r="C342" s="6">
-        <v>60</v>
+        <v>421.08</v>
       </c>
       <c r="D342" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -6331,7 +6337,7 @@
         <v>175</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D343" t="s">
         <v>148</v>
@@ -6342,21 +6348,21 @@
         <v>175</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
+      </c>
+      <c r="C344" s="6">
+        <v>60</v>
       </c>
       <c r="D344" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>175</v>
       </c>
-      <c r="B345" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C345" s="6">
-        <v>15.25</v>
+      <c r="B345" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="D345" t="s">
         <v>148</v>
@@ -6366,11 +6372,8 @@
       <c r="A346" t="s">
         <v>175</v>
       </c>
-      <c r="B346" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C346" s="6">
-        <v>18.899999999999999</v>
+      <c r="B346" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="D346" t="s">
         <v>148</v>
@@ -6380,11 +6383,11 @@
       <c r="A347" t="s">
         <v>175</v>
       </c>
-      <c r="B347" s="3" t="s">
-        <v>96</v>
+      <c r="B347" s="3">
+        <v>4430</v>
       </c>
       <c r="C347" s="6">
-        <v>193</v>
+        <v>15.25</v>
       </c>
       <c r="D347" t="s">
         <v>148</v>
@@ -6394,8 +6397,11 @@
       <c r="A348" t="s">
         <v>175</v>
       </c>
-      <c r="B348" s="3" t="s">
-        <v>97</v>
+      <c r="B348" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C348" s="6">
+        <v>18.899999999999999</v>
       </c>
       <c r="D348" t="s">
         <v>148</v>
@@ -6405,11 +6411,11 @@
       <c r="A349" t="s">
         <v>175</v>
       </c>
-      <c r="B349" s="3">
-        <v>4642</v>
+      <c r="B349" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C349" s="6">
-        <v>20.8</v>
+        <v>193</v>
       </c>
       <c r="D349" t="s">
         <v>148</v>
@@ -6420,7 +6426,7 @@
         <v>175</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D350" t="s">
         <v>148</v>
@@ -6431,10 +6437,10 @@
         <v>175</v>
       </c>
       <c r="B351" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C351" s="6">
-        <v>24.7</v>
+        <v>20.8</v>
       </c>
       <c r="D351" t="s">
         <v>148</v>
@@ -6444,11 +6450,8 @@
       <c r="A352" t="s">
         <v>175</v>
       </c>
-      <c r="B352" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C352" s="6">
-        <v>26.8</v>
+      <c r="B352" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="D352" t="s">
         <v>148</v>
@@ -6458,11 +6461,11 @@
       <c r="A353" t="s">
         <v>175</v>
       </c>
-      <c r="B353" s="3" t="s">
-        <v>99</v>
+      <c r="B353" s="3">
+        <v>4660</v>
       </c>
       <c r="C353" s="6">
-        <v>115</v>
+        <v>24.7</v>
       </c>
       <c r="D353" t="s">
         <v>148</v>
@@ -6473,10 +6476,10 @@
         <v>175</v>
       </c>
       <c r="B354" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C354" s="6">
-        <v>27.05</v>
+        <v>26.8</v>
       </c>
       <c r="D354" t="s">
         <v>148</v>
@@ -6487,10 +6490,10 @@
         <v>175</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C355" s="6">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="D355" t="s">
         <v>148</v>
@@ -6500,14 +6503,14 @@
       <c r="A356" t="s">
         <v>175</v>
       </c>
-      <c r="B356" s="3" t="s">
-        <v>180</v>
+      <c r="B356" s="3">
+        <v>6660</v>
       </c>
       <c r="C356" s="6">
-        <v>30.5</v>
+        <v>27.05</v>
       </c>
       <c r="D356" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -6515,13 +6518,13 @@
         <v>175</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="C357" s="6">
-        <v>12.75</v>
+        <v>160</v>
       </c>
       <c r="D357" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -6529,13 +6532,13 @@
         <v>175</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="C358" s="6">
-        <v>12.75</v>
+        <v>30.5</v>
       </c>
       <c r="D358" t="s">
-        <v>270</v>
+        <v>149</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -6543,10 +6546,10 @@
         <v>175</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C359" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D359" t="s">
         <v>270</v>
@@ -6557,10 +6560,10 @@
         <v>175</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C360" s="6">
-        <v>10.3</v>
+        <v>12.75</v>
       </c>
       <c r="D360" t="s">
         <v>270</v>
@@ -6571,10 +6574,10 @@
         <v>175</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C361" s="6">
-        <v>11.85</v>
+        <v>13.25</v>
       </c>
       <c r="D361" t="s">
         <v>270</v>
@@ -6585,10 +6588,10 @@
         <v>175</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C362" s="6">
-        <v>12.75</v>
+        <v>10.3</v>
       </c>
       <c r="D362" t="s">
         <v>270</v>
@@ -6599,10 +6602,10 @@
         <v>175</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C363" s="6">
-        <v>10.3</v>
+        <v>11.85</v>
       </c>
       <c r="D363" t="s">
         <v>270</v>
@@ -6613,10 +6616,10 @@
         <v>175</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C364" s="6">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
       <c r="D364" t="s">
         <v>270</v>
@@ -6627,10 +6630,10 @@
         <v>175</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C365" s="6">
-        <v>12.75</v>
+        <v>10.3</v>
       </c>
       <c r="D365" t="s">
         <v>270</v>
@@ -6641,13 +6644,13 @@
         <v>175</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>107</v>
+        <v>263</v>
       </c>
       <c r="C366" s="6">
-        <v>21.5</v>
+        <v>13.25</v>
       </c>
       <c r="D366" t="s">
-        <v>152</v>
+        <v>270</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -6655,13 +6658,13 @@
         <v>175</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>108</v>
+        <v>272</v>
       </c>
       <c r="C367" s="6">
-        <v>22.5</v>
+        <v>12.75</v>
       </c>
       <c r="D367" t="s">
-        <v>152</v>
+        <v>270</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -6669,10 +6672,10 @@
         <v>175</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C368" s="6">
-        <v>10.5</v>
+        <v>21.5</v>
       </c>
       <c r="D368" t="s">
         <v>152</v>
@@ -6683,10 +6686,10 @@
         <v>175</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C369" s="6">
-        <v>10.5</v>
+        <v>22.5</v>
       </c>
       <c r="D369" t="s">
         <v>152</v>
@@ -6697,7 +6700,7 @@
         <v>175</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C370" s="6">
         <v>10.5</v>
@@ -6711,10 +6714,13 @@
         <v>175</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>277</v>
+        <v>116</v>
+      </c>
+      <c r="C371" s="6">
+        <v>10.5</v>
       </c>
       <c r="D371" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -6722,13 +6728,13 @@
         <v>175</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>278</v>
+        <v>117</v>
       </c>
       <c r="C372" s="6">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="D372" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -6736,7 +6742,7 @@
         <v>175</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D373" t="s">
         <v>173</v>
@@ -6747,13 +6753,13 @@
         <v>175</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>118</v>
+        <v>278</v>
       </c>
       <c r="C374" s="6">
-        <v>23.15</v>
+        <v>23</v>
       </c>
       <c r="D374" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -6761,13 +6767,10 @@
         <v>175</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C375" s="6">
-        <v>42.65</v>
+        <v>279</v>
       </c>
       <c r="D375" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -6775,10 +6778,10 @@
         <v>175</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C376" s="6">
-        <v>82</v>
+        <v>23.15</v>
       </c>
       <c r="D376" t="s">
         <v>153</v>
@@ -6789,10 +6792,10 @@
         <v>175</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C377" s="6">
-        <v>33.5</v>
+        <v>42.65</v>
       </c>
       <c r="D377" t="s">
         <v>153</v>
@@ -6803,10 +6806,10 @@
         <v>175</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C378" s="6">
-        <v>60.9</v>
+        <v>82</v>
       </c>
       <c r="D378" t="s">
         <v>153</v>
@@ -6817,10 +6820,10 @@
         <v>175</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C379" s="6">
-        <v>118</v>
+        <v>33.5</v>
       </c>
       <c r="D379" t="s">
         <v>153</v>
@@ -6831,10 +6834,10 @@
         <v>175</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C380" s="6">
-        <v>16</v>
+        <v>60.9</v>
       </c>
       <c r="D380" t="s">
         <v>153</v>
@@ -6845,10 +6848,10 @@
         <v>175</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C381" s="6">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="D381" t="s">
         <v>153</v>
@@ -6859,10 +6862,10 @@
         <v>175</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C382" s="6">
-        <v>21.32</v>
+        <v>16</v>
       </c>
       <c r="D382" t="s">
         <v>153</v>
@@ -6873,13 +6876,13 @@
         <v>175</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C383" s="6">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D383" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -6887,10 +6890,13 @@
         <v>175</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="C384" s="6">
+        <v>21.32</v>
       </c>
       <c r="D384" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -6898,10 +6904,10 @@
         <v>175</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C385" s="6">
-        <v>13.42</v>
+        <v>26</v>
       </c>
       <c r="D385" t="s">
         <v>154</v>
@@ -6912,7 +6918,7 @@
         <v>175</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D386" t="s">
         <v>154</v>
@@ -6923,7 +6929,10 @@
         <v>175</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
+      </c>
+      <c r="C387" s="6">
+        <v>13.42</v>
       </c>
       <c r="D387" t="s">
         <v>154</v>
@@ -6934,41 +6943,35 @@
         <v>175</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C388" s="6">
-        <v>9.5399999999999991</v>
+        <v>130</v>
       </c>
       <c r="D388" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A391" t="s">
-        <v>181</v>
-      </c>
-      <c r="B391" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C391" s="6">
-        <v>14.5</v>
-      </c>
-      <c r="D391" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A392" t="s">
-        <v>181</v>
-      </c>
-      <c r="B392" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C392" s="6">
-        <v>24.99</v>
-      </c>
-      <c r="D392" t="s">
-        <v>138</v>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>175</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D389" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>175</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C390" s="6">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="D390" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -6976,13 +6979,13 @@
         <v>181</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>7</v>
+        <v>320</v>
       </c>
       <c r="C393" s="6">
-        <v>34.99</v>
+        <v>14.5</v>
       </c>
       <c r="D393" t="s">
-        <v>138</v>
+        <v>320</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -6990,13 +6993,13 @@
         <v>181</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C394" s="6">
-        <v>19.989999999999998</v>
+        <v>24.99</v>
       </c>
       <c r="D394" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -7004,13 +7007,13 @@
         <v>181</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C395" s="6">
-        <v>29.99</v>
+        <v>34.99</v>
       </c>
       <c r="D395" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -7018,13 +7021,13 @@
         <v>181</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C396" s="6">
-        <v>189.99</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D396" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -7032,13 +7035,13 @@
         <v>181</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C397" s="6">
-        <v>229.99</v>
+        <v>29.99</v>
       </c>
       <c r="D397" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -7046,10 +7049,10 @@
         <v>181</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="C398" s="6">
-        <v>299.99</v>
+        <v>189.99</v>
       </c>
       <c r="D398" t="s">
         <v>142</v>
@@ -7060,10 +7063,10 @@
         <v>181</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C399" s="6">
-        <v>189.99</v>
+        <v>229.99</v>
       </c>
       <c r="D399" t="s">
         <v>142</v>
@@ -7074,10 +7077,10 @@
         <v>181</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="C400" s="6">
-        <v>229</v>
+        <v>299.99</v>
       </c>
       <c r="D400" t="s">
         <v>142</v>
@@ -7088,10 +7091,10 @@
         <v>181</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="C401" s="6">
-        <v>299.99</v>
+        <v>189.99</v>
       </c>
       <c r="D401" t="s">
         <v>142</v>
@@ -7102,10 +7105,10 @@
         <v>181</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C402" s="6">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="D402" t="s">
         <v>142</v>
@@ -7116,10 +7119,10 @@
         <v>181</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>31</v>
+        <v>183</v>
       </c>
       <c r="C403" s="6">
-        <v>345</v>
+        <v>299.99</v>
       </c>
       <c r="D403" t="s">
         <v>142</v>
@@ -7130,10 +7133,10 @@
         <v>181</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C404" s="6">
-        <v>409</v>
+        <v>309</v>
       </c>
       <c r="D404" t="s">
         <v>142</v>
@@ -7144,10 +7147,10 @@
         <v>181</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C405" s="6">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="D405" t="s">
         <v>142</v>
@@ -7158,10 +7161,10 @@
         <v>181</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="C406" s="6">
-        <v>389.99</v>
+        <v>409</v>
       </c>
       <c r="D406" t="s">
         <v>142</v>
@@ -7172,10 +7175,10 @@
         <v>181</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C407" s="6">
-        <v>399.99</v>
+        <v>389</v>
       </c>
       <c r="D407" t="s">
         <v>142</v>
@@ -7186,10 +7189,10 @@
         <v>181</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C408" s="6">
-        <v>399.99</v>
+        <v>389.99</v>
       </c>
       <c r="D408" t="s">
         <v>142</v>
@@ -7200,10 +7203,10 @@
         <v>181</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C409" s="6">
-        <v>89.23</v>
+        <v>399.99</v>
       </c>
       <c r="D409" t="s">
         <v>142</v>
@@ -7214,7 +7217,10 @@
         <v>181</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>36</v>
+        <v>185</v>
+      </c>
+      <c r="C410" s="6">
+        <v>399.99</v>
       </c>
       <c r="D410" t="s">
         <v>142</v>
@@ -7225,10 +7231,10 @@
         <v>181</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C411" s="6">
-        <v>219.99</v>
+        <v>89.23</v>
       </c>
       <c r="D411" t="s">
         <v>142</v>
@@ -7239,10 +7245,7 @@
         <v>181</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C412" s="6">
-        <v>429</v>
+        <v>36</v>
       </c>
       <c r="D412" t="s">
         <v>142</v>
@@ -7253,10 +7256,10 @@
         <v>181</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="C413" s="6">
-        <v>439</v>
+        <v>219.99</v>
       </c>
       <c r="D413" t="s">
         <v>142</v>
@@ -7267,10 +7270,10 @@
         <v>181</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C414" s="6">
-        <v>199</v>
+        <v>429</v>
       </c>
       <c r="D414" t="s">
         <v>142</v>
@@ -7281,10 +7284,10 @@
         <v>181</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C415" s="6">
-        <v>249</v>
+        <v>439</v>
       </c>
       <c r="D415" t="s">
         <v>142</v>
@@ -7295,10 +7298,10 @@
         <v>181</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C416" s="6">
-        <v>670</v>
+        <v>199</v>
       </c>
       <c r="D416" t="s">
         <v>142</v>
@@ -7309,10 +7312,10 @@
         <v>181</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C417" s="6">
-        <v>49.99</v>
+        <v>249</v>
       </c>
       <c r="D417" t="s">
         <v>142</v>
@@ -7323,10 +7326,10 @@
         <v>181</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C418" s="6">
-        <v>49.99</v>
+        <v>670</v>
       </c>
       <c r="D418" t="s">
         <v>142</v>
@@ -7337,13 +7340,13 @@
         <v>181</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>335</v>
+        <v>191</v>
       </c>
       <c r="C419" s="6">
-        <v>15.99</v>
+        <v>49.99</v>
       </c>
       <c r="D419" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -7351,13 +7354,13 @@
         <v>181</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>336</v>
+        <v>192</v>
       </c>
       <c r="C420" s="6">
-        <v>29.99</v>
+        <v>49.99</v>
       </c>
       <c r="D420" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -7365,10 +7368,10 @@
         <v>181</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C421" s="6">
-        <v>16.989999999999998</v>
+        <v>15.99</v>
       </c>
       <c r="D421" t="s">
         <v>144</v>
@@ -7379,7 +7382,7 @@
         <v>181</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C422" s="6">
         <v>29.99</v>
@@ -7393,10 +7396,10 @@
         <v>181</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>193</v>
+        <v>333</v>
       </c>
       <c r="C423" s="6">
-        <v>11.49</v>
+        <v>16.989999999999998</v>
       </c>
       <c r="D423" t="s">
         <v>144</v>
@@ -7407,10 +7410,10 @@
         <v>181</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="C424" s="6">
-        <v>18.95</v>
+        <v>29.99</v>
       </c>
       <c r="D424" t="s">
         <v>144</v>
@@ -7421,10 +7424,10 @@
         <v>181</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C425" s="6">
-        <v>39.99</v>
+        <v>11.49</v>
       </c>
       <c r="D425" t="s">
         <v>144</v>
@@ -7434,11 +7437,11 @@
       <c r="A426" t="s">
         <v>181</v>
       </c>
-      <c r="B426" s="3">
-        <v>6102</v>
+      <c r="B426" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C426" s="6">
-        <v>44.5</v>
+        <v>18.95</v>
       </c>
       <c r="D426" t="s">
         <v>144</v>
@@ -7449,10 +7452,10 @@
         <v>181</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C427" s="6">
-        <v>112</v>
+        <v>39.99</v>
       </c>
       <c r="D427" t="s">
         <v>144</v>
@@ -7462,11 +7465,11 @@
       <c r="A428" t="s">
         <v>181</v>
       </c>
-      <c r="B428" s="3" t="s">
-        <v>197</v>
+      <c r="B428" s="3">
+        <v>6102</v>
       </c>
       <c r="C428" s="6">
-        <v>139</v>
+        <v>44.5</v>
       </c>
       <c r="D428" t="s">
         <v>144</v>
@@ -7477,10 +7480,10 @@
         <v>181</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C429" s="6">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D429" t="s">
         <v>144</v>
@@ -7491,7 +7494,10 @@
         <v>181</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
+      </c>
+      <c r="C430" s="6">
+        <v>139</v>
       </c>
       <c r="D430" t="s">
         <v>144</v>
@@ -7502,7 +7508,10 @@
         <v>181</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
+      </c>
+      <c r="C431" s="6">
+        <v>139</v>
       </c>
       <c r="D431" t="s">
         <v>144</v>
@@ -7513,10 +7522,7 @@
         <v>181</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C432" s="6">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D432" t="s">
         <v>144</v>
@@ -7527,7 +7533,7 @@
         <v>181</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D433" t="s">
         <v>144</v>
@@ -7538,7 +7544,10 @@
         <v>181</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
+      </c>
+      <c r="C434" s="6">
+        <v>209</v>
       </c>
       <c r="D434" t="s">
         <v>144</v>
@@ -7549,10 +7558,7 @@
         <v>181</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C435" s="6">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D435" t="s">
         <v>144</v>
@@ -7563,10 +7569,7 @@
         <v>181</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C436" s="6">
-        <v>299.99</v>
+        <v>203</v>
       </c>
       <c r="D436" t="s">
         <v>144</v>
@@ -7577,10 +7580,10 @@
         <v>181</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C437" s="6">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="D437" t="s">
         <v>144</v>
@@ -7591,10 +7594,10 @@
         <v>181</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C438" s="6">
-        <v>245</v>
+        <v>299.99</v>
       </c>
       <c r="D438" t="s">
         <v>144</v>
@@ -7605,10 +7608,10 @@
         <v>181</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C439" s="6">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="D439" t="s">
         <v>144</v>
@@ -7619,10 +7622,10 @@
         <v>181</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C440" s="6">
-        <v>399</v>
+        <v>245</v>
       </c>
       <c r="D440" t="s">
         <v>144</v>
@@ -7633,10 +7636,10 @@
         <v>181</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C441" s="6">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D441" t="s">
         <v>144</v>
@@ -7647,10 +7650,10 @@
         <v>181</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C442" s="6">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="D442" t="s">
         <v>144</v>
@@ -7661,7 +7664,7 @@
         <v>181</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C443" s="6">
         <v>209</v>
@@ -7675,10 +7678,10 @@
         <v>181</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C444" s="6">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="D444" t="s">
         <v>144</v>
@@ -7689,10 +7692,10 @@
         <v>181</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C445" s="6">
-        <v>315</v>
+        <v>209</v>
       </c>
       <c r="D445" t="s">
         <v>144</v>
@@ -7703,10 +7706,10 @@
         <v>181</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C446" s="6">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="D446" t="s">
         <v>144</v>
@@ -7717,10 +7720,10 @@
         <v>181</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C447" s="6">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="D447" t="s">
         <v>144</v>
@@ -7731,10 +7734,10 @@
         <v>181</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C448" s="6">
-        <v>420</v>
+        <v>265</v>
       </c>
       <c r="D448" t="s">
         <v>144</v>
@@ -7745,10 +7748,10 @@
         <v>181</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C449" s="6">
-        <v>315</v>
+        <v>251</v>
       </c>
       <c r="D449" t="s">
         <v>144</v>
@@ -7759,10 +7762,10 @@
         <v>181</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C450" s="6">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="D450" t="s">
         <v>144</v>
@@ -7773,10 +7776,10 @@
         <v>181</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C451" s="6">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="D451" t="s">
         <v>144</v>
@@ -7787,13 +7790,13 @@
         <v>181</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>54</v>
+        <v>219</v>
       </c>
       <c r="C452" s="6">
-        <v>55.99</v>
+        <v>365</v>
       </c>
       <c r="D452" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
@@ -7801,13 +7804,13 @@
         <v>181</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="C453" s="6">
-        <v>39.99</v>
+        <v>285</v>
       </c>
       <c r="D453" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
@@ -7815,10 +7818,10 @@
         <v>181</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C454" s="6">
-        <v>68</v>
+        <v>55.99</v>
       </c>
       <c r="D454" t="s">
         <v>145</v>
@@ -7829,10 +7832,10 @@
         <v>181</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C455" s="6">
-        <v>129</v>
+        <v>39.99</v>
       </c>
       <c r="D455" t="s">
         <v>145</v>
@@ -7843,10 +7846,10 @@
         <v>181</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>255</v>
+        <v>57</v>
       </c>
       <c r="C456" s="6">
-        <v>30.99</v>
+        <v>68</v>
       </c>
       <c r="D456" t="s">
         <v>145</v>
@@ -7857,10 +7860,10 @@
         <v>181</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="C457" s="6">
-        <v>42.99</v>
+        <v>129</v>
       </c>
       <c r="D457" t="s">
         <v>145</v>
@@ -7871,10 +7874,10 @@
         <v>181</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C458" s="6">
-        <v>159</v>
+        <v>30.99</v>
       </c>
       <c r="D458" t="s">
         <v>145</v>
@@ -7885,10 +7888,10 @@
         <v>181</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="C459" s="6">
-        <v>49.99</v>
+        <v>42.99</v>
       </c>
       <c r="D459" t="s">
         <v>145</v>
@@ -7899,10 +7902,10 @@
         <v>181</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="C460" s="6">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="D460" t="s">
         <v>145</v>
@@ -7913,13 +7916,13 @@
         <v>181</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>59</v>
+        <v>274</v>
       </c>
       <c r="C461" s="6">
-        <v>47.99</v>
+        <v>49.99</v>
       </c>
       <c r="D461" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -7927,13 +7930,13 @@
         <v>181</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>221</v>
+        <v>275</v>
       </c>
       <c r="C462" s="6">
-        <v>34.99</v>
+        <v>129</v>
       </c>
       <c r="D462" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -7941,13 +7944,13 @@
         <v>181</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C463" s="6">
-        <v>89.99</v>
+        <v>47.99</v>
       </c>
       <c r="D463" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -7955,13 +7958,13 @@
         <v>181</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="C464" s="6">
-        <v>45</v>
+        <v>34.99</v>
       </c>
       <c r="D464" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -7969,13 +7972,13 @@
         <v>181</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="C465" s="6">
-        <v>88</v>
+        <v>89.99</v>
       </c>
       <c r="D465" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -7983,10 +7986,10 @@
         <v>181</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="C466" s="6">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="D466" t="s">
         <v>149</v>
@@ -7997,13 +8000,13 @@
         <v>181</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="C467" s="6">
-        <v>79.989999999999995</v>
+        <v>88</v>
       </c>
       <c r="D467" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -8011,13 +8014,13 @@
         <v>181</v>
       </c>
       <c r="B468" s="3" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="C468" s="6">
-        <v>7.95</v>
+        <v>125</v>
       </c>
       <c r="D468" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -8025,13 +8028,13 @@
         <v>181</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>277</v>
+        <v>105</v>
       </c>
       <c r="C469" s="6">
-        <v>18.95</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="D469" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -8039,10 +8042,10 @@
         <v>181</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C470" s="6">
-        <v>36.950000000000003</v>
+        <v>7.95</v>
       </c>
       <c r="D470" t="s">
         <v>173</v>
@@ -8053,13 +8056,13 @@
         <v>181</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>127</v>
+        <v>277</v>
       </c>
       <c r="C471" s="6">
-        <v>39.99</v>
+        <v>18.95</v>
       </c>
       <c r="D471" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -8067,13 +8070,13 @@
         <v>181</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="C472" s="6">
-        <v>19.5</v>
+        <v>36.950000000000003</v>
       </c>
       <c r="D472" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -8081,13 +8084,13 @@
         <v>181</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>321</v>
+        <v>127</v>
       </c>
       <c r="C473" s="6">
-        <v>110</v>
+        <v>39.99</v>
       </c>
       <c r="D473" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -8095,10 +8098,10 @@
         <v>181</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="C474" s="6">
-        <v>98.45</v>
+        <v>19.5</v>
       </c>
       <c r="D474" t="s">
         <v>139</v>
@@ -8109,10 +8112,10 @@
         <v>181</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C475" s="6">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D475" t="s">
         <v>139</v>
@@ -8123,10 +8126,10 @@
         <v>181</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C476" s="6">
-        <v>199</v>
+        <v>98.45</v>
       </c>
       <c r="D476" t="s">
         <v>139</v>
@@ -8137,10 +8140,10 @@
         <v>181</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C477" s="6">
-        <v>169.99</v>
+        <v>139</v>
       </c>
       <c r="D477" t="s">
         <v>139</v>
@@ -8151,10 +8154,10 @@
         <v>181</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C478" s="6">
-        <v>239.08</v>
+        <v>199</v>
       </c>
       <c r="D478" t="s">
         <v>139</v>
@@ -8165,10 +8168,10 @@
         <v>181</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C479" s="6">
-        <v>219</v>
+        <v>169.99</v>
       </c>
       <c r="D479" t="s">
         <v>139</v>
@@ -8179,10 +8182,10 @@
         <v>181</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C480" s="6">
-        <v>189.99</v>
+        <v>239.08</v>
       </c>
       <c r="D480" t="s">
         <v>139</v>
@@ -8193,10 +8196,10 @@
         <v>181</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C481" s="6">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="D481" t="s">
         <v>139</v>
@@ -8207,10 +8210,10 @@
         <v>181</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C482" s="6">
-        <v>297</v>
+        <v>189.99</v>
       </c>
       <c r="D482" t="s">
         <v>139</v>
@@ -8221,40 +8224,40 @@
         <v>181</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C483" s="6">
-        <v>322</v>
+        <v>248</v>
       </c>
       <c r="D483" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
-        <v>224</v>
-      </c>
-      <c r="B493" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C493" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D493" t="s">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>181</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C484" s="6">
+        <v>297</v>
+      </c>
+      <c r="D484" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
-        <v>224</v>
-      </c>
-      <c r="B494" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C494" s="6">
-        <v>79.47</v>
-      </c>
-      <c r="D494" t="s">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>181</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C485" s="6">
+        <v>322</v>
+      </c>
+      <c r="D485" t="s">
         <v>139</v>
       </c>
     </row>
@@ -8263,10 +8266,10 @@
         <v>224</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C495" s="6">
-        <v>92.85</v>
+        <v>42.75</v>
       </c>
       <c r="D495" t="s">
         <v>139</v>
@@ -8276,28 +8279,28 @@
       <c r="A496" t="s">
         <v>224</v>
       </c>
-      <c r="B496" s="3">
-        <v>4430</v>
+      <c r="B496" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="C496" s="6">
-        <v>15.25</v>
+        <v>79.47</v>
       </c>
       <c r="D496" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>224</v>
       </c>
-      <c r="B497" s="3">
-        <v>4442</v>
+      <c r="B497" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C497" s="6">
-        <v>18.899999999999999</v>
+        <v>92.85</v>
       </c>
       <c r="D497" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -8305,10 +8308,10 @@
         <v>224</v>
       </c>
       <c r="B498" s="3">
-        <v>6642</v>
+        <v>4430</v>
       </c>
       <c r="C498" s="6">
-        <v>26.8</v>
+        <v>15.25</v>
       </c>
       <c r="D498" t="s">
         <v>148</v>
@@ -8319,41 +8322,41 @@
         <v>224</v>
       </c>
       <c r="B499" s="3">
-        <v>6660</v>
+        <v>4442</v>
       </c>
       <c r="C499" s="6">
-        <v>27.05</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D499" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>228</v>
-      </c>
-      <c r="B502" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C502" s="6">
-        <v>47.95</v>
-      </c>
-      <c r="D502" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>228</v>
-      </c>
-      <c r="B503" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C503" s="6">
-        <v>59.07</v>
-      </c>
-      <c r="D503" t="s">
-        <v>139</v>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>224</v>
+      </c>
+      <c r="B500" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C500" s="6">
+        <v>26.8</v>
+      </c>
+      <c r="D500" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>224</v>
+      </c>
+      <c r="B501" s="3">
+        <v>6660</v>
+      </c>
+      <c r="C501" s="6">
+        <v>27.05</v>
+      </c>
+      <c r="D501" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -8361,10 +8364,10 @@
         <v>228</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C504" s="6">
-        <v>83.8</v>
+        <v>47.95</v>
       </c>
       <c r="D504" t="s">
         <v>139</v>
@@ -8375,10 +8378,10 @@
         <v>228</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C505" s="6">
-        <v>115.4</v>
+        <v>59.07</v>
       </c>
       <c r="D505" t="s">
         <v>139</v>
@@ -8389,10 +8392,10 @@
         <v>228</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C506" s="6">
-        <v>107.15</v>
+        <v>83.8</v>
       </c>
       <c r="D506" t="s">
         <v>139</v>
@@ -8403,13 +8406,13 @@
         <v>228</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C507" s="6">
-        <v>13</v>
+        <v>115.4</v>
       </c>
       <c r="D507" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
@@ -8417,13 +8420,13 @@
         <v>228</v>
       </c>
       <c r="B508" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C508" s="6">
-        <v>17</v>
+        <v>107.15</v>
       </c>
       <c r="D508" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
@@ -8431,41 +8434,41 @@
         <v>228</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="C509" s="6">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D509" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>228</v>
       </c>
-      <c r="B510" s="3">
-        <v>4430</v>
+      <c r="B510" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C510" s="6">
-        <v>15.25</v>
+        <v>17</v>
       </c>
       <c r="D510" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>228</v>
       </c>
-      <c r="B511" s="3">
-        <v>4442</v>
+      <c r="B511" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C511" s="6">
-        <v>18.899999999999999</v>
+        <v>30</v>
       </c>
       <c r="D511" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
@@ -8473,10 +8476,10 @@
         <v>228</v>
       </c>
       <c r="B512" s="3">
-        <v>6642</v>
+        <v>4430</v>
       </c>
       <c r="C512" s="6">
-        <v>26.8</v>
+        <v>15.25</v>
       </c>
       <c r="D512" t="s">
         <v>148</v>
@@ -8486,42 +8489,42 @@
       <c r="A513" t="s">
         <v>228</v>
       </c>
-      <c r="B513" s="3" t="s">
+      <c r="B513" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C513" s="6">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D513" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>228</v>
+      </c>
+      <c r="B514" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C514" s="6">
+        <v>26.8</v>
+      </c>
+      <c r="D514" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>228</v>
+      </c>
+      <c r="B515" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C513" s="6">
+      <c r="C515" s="6">
         <v>39.950000000000003</v>
       </c>
-      <c r="D513" t="s">
+      <c r="D515" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A516" t="s">
-        <v>229</v>
-      </c>
-      <c r="B516" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C516" s="6">
-        <v>9.92</v>
-      </c>
-      <c r="D516" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A517" t="s">
-        <v>229</v>
-      </c>
-      <c r="B517" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C517" s="6">
-        <v>47.95</v>
-      </c>
-      <c r="D517" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
@@ -8529,13 +8532,13 @@
         <v>229</v>
       </c>
       <c r="B518" s="3" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="C518" s="6">
-        <v>55.73</v>
+        <v>9.92</v>
       </c>
       <c r="D518" t="s">
-        <v>139</v>
+        <v>231</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
@@ -8543,10 +8546,10 @@
         <v>229</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C519" s="6">
-        <v>79.06</v>
+        <v>47.95</v>
       </c>
       <c r="D519" t="s">
         <v>139</v>
@@ -8557,10 +8560,10 @@
         <v>229</v>
       </c>
       <c r="B520" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C520" s="6">
-        <v>108.86</v>
+        <v>55.73</v>
       </c>
       <c r="D520" t="s">
         <v>139</v>
@@ -8571,10 +8574,10 @@
         <v>229</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C521" s="6">
-        <v>101.09</v>
+        <v>79.06</v>
       </c>
       <c r="D521" t="s">
         <v>139</v>
@@ -8585,10 +8588,10 @@
         <v>229</v>
       </c>
       <c r="B522" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C522" s="6">
-        <v>160.69999999999999</v>
+        <v>108.86</v>
       </c>
       <c r="D522" t="s">
         <v>139</v>
@@ -8599,10 +8602,10 @@
         <v>229</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C523" s="6">
-        <v>121.82</v>
+        <v>101.09</v>
       </c>
       <c r="D523" t="s">
         <v>139</v>
@@ -8613,10 +8616,10 @@
         <v>229</v>
       </c>
       <c r="B524" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C524" s="6">
-        <v>122.49</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="D524" t="s">
         <v>139</v>
@@ -8627,7 +8630,10 @@
         <v>229</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="C525" s="6">
+        <v>121.82</v>
       </c>
       <c r="D525" t="s">
         <v>139</v>
@@ -8638,7 +8644,10 @@
         <v>229</v>
       </c>
       <c r="B526" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="C526" s="6">
+        <v>122.49</v>
       </c>
       <c r="D526" t="s">
         <v>139</v>
@@ -8649,7 +8658,7 @@
         <v>229</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D527" t="s">
         <v>139</v>
@@ -8660,10 +8669,7 @@
         <v>229</v>
       </c>
       <c r="B528" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C528" s="6">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D528" t="s">
         <v>139</v>
@@ -8674,10 +8680,7 @@
         <v>229</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C529" s="6">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D529" t="s">
         <v>139</v>
@@ -8688,10 +8691,10 @@
         <v>229</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C530" s="6">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D530" t="s">
         <v>139</v>
@@ -8702,32 +8705,35 @@
         <v>229</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>92</v>
+        <v>226</v>
+      </c>
+      <c r="C531" s="6">
+        <v>67</v>
       </c>
       <c r="D531" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>229</v>
       </c>
-      <c r="B532" s="3">
-        <v>4430</v>
+      <c r="B532" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C532" s="6">
+        <v>79</v>
       </c>
       <c r="D532" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>229</v>
       </c>
-      <c r="B533" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C533" s="6">
-        <v>15</v>
+      <c r="B533" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D533" t="s">
         <v>148</v>
@@ -8737,11 +8743,8 @@
       <c r="A534" t="s">
         <v>229</v>
       </c>
-      <c r="B534" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C534" s="6">
-        <v>171</v>
+      <c r="B534" s="3">
+        <v>4430</v>
       </c>
       <c r="D534" t="s">
         <v>148</v>
@@ -8751,8 +8754,11 @@
       <c r="A535" t="s">
         <v>229</v>
       </c>
-      <c r="B535" s="3" t="s">
-        <v>97</v>
+      <c r="B535" s="3">
+        <v>4442</v>
+      </c>
+      <c r="C535" s="6">
+        <v>15</v>
       </c>
       <c r="D535" t="s">
         <v>148</v>
@@ -8762,11 +8768,11 @@
       <c r="A536" t="s">
         <v>229</v>
       </c>
-      <c r="B536" s="3">
-        <v>4642</v>
+      <c r="B536" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C536" s="6">
-        <v>16.5</v>
+        <v>171</v>
       </c>
       <c r="D536" t="s">
         <v>148</v>
@@ -8777,10 +8783,7 @@
         <v>229</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C537" s="6">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D537" t="s">
         <v>148</v>
@@ -8791,10 +8794,10 @@
         <v>229</v>
       </c>
       <c r="B538" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C538" s="6">
-        <v>20.25</v>
+        <v>16.5</v>
       </c>
       <c r="D538" t="s">
         <v>148</v>
@@ -8804,8 +8807,11 @@
       <c r="A539" t="s">
         <v>229</v>
       </c>
-      <c r="B539" s="3">
-        <v>6630</v>
+      <c r="B539" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C539" s="6">
+        <v>126</v>
       </c>
       <c r="D539" t="s">
         <v>148</v>
@@ -8816,10 +8822,10 @@
         <v>229</v>
       </c>
       <c r="B540" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C540" s="6">
-        <v>18.5</v>
+        <v>20.25</v>
       </c>
       <c r="D540" t="s">
         <v>148</v>
@@ -8829,11 +8835,8 @@
       <c r="A541" t="s">
         <v>229</v>
       </c>
-      <c r="B541" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C541" s="6">
-        <v>103.5</v>
+      <c r="B541" s="3">
+        <v>6630</v>
       </c>
       <c r="D541" t="s">
         <v>148</v>
@@ -8844,10 +8847,10 @@
         <v>229</v>
       </c>
       <c r="B542" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C542" s="6">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="D542" t="s">
         <v>148</v>
@@ -8858,10 +8861,10 @@
         <v>229</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C543" s="6">
-        <v>126</v>
+        <v>103.5</v>
       </c>
       <c r="D543" t="s">
         <v>148</v>
@@ -8872,34 +8875,37 @@
         <v>229</v>
       </c>
       <c r="B544" s="3">
-        <v>8860</v>
+        <v>6660</v>
+      </c>
+      <c r="C544" s="6">
+        <v>22.5</v>
       </c>
       <c r="D544" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A547" t="s">
-        <v>232</v>
-      </c>
-      <c r="B547" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D547" t="s">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>229</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C545" s="6">
+        <v>126</v>
+      </c>
+      <c r="D545" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A548" t="s">
-        <v>232</v>
-      </c>
-      <c r="B548" s="3">
-        <v>4430</v>
-      </c>
-      <c r="C548" s="6">
-        <v>15.25</v>
-      </c>
-      <c r="D548" t="s">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>229</v>
+      </c>
+      <c r="B546" s="3">
+        <v>8860</v>
+      </c>
+      <c r="D546" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8907,11 +8913,8 @@
       <c r="A549" t="s">
         <v>232</v>
       </c>
-      <c r="B549" s="3">
-        <v>4442</v>
-      </c>
-      <c r="C549" s="6">
-        <v>15</v>
+      <c r="B549" s="3" t="s">
+        <v>233</v>
       </c>
       <c r="D549" t="s">
         <v>148</v>
@@ -8921,11 +8924,11 @@
       <c r="A550" t="s">
         <v>232</v>
       </c>
-      <c r="B550" s="3" t="s">
-        <v>96</v>
+      <c r="B550" s="3">
+        <v>4430</v>
       </c>
       <c r="C550" s="6">
-        <v>171</v>
+        <v>15.25</v>
       </c>
       <c r="D550" t="s">
         <v>148</v>
@@ -8935,11 +8938,11 @@
       <c r="A551" t="s">
         <v>232</v>
       </c>
-      <c r="B551" s="3" t="s">
-        <v>97</v>
+      <c r="B551" s="3">
+        <v>4442</v>
       </c>
       <c r="C551" s="6">
-        <v>972</v>
+        <v>15</v>
       </c>
       <c r="D551" t="s">
         <v>148</v>
@@ -8949,11 +8952,11 @@
       <c r="A552" t="s">
         <v>232</v>
       </c>
-      <c r="B552" s="3">
-        <v>4642</v>
+      <c r="B552" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="C552" s="6">
-        <v>16.5</v>
+        <v>171</v>
       </c>
       <c r="D552" t="s">
         <v>148</v>
@@ -8964,10 +8967,10 @@
         <v>232</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C553" s="6">
-        <v>126</v>
+        <v>972</v>
       </c>
       <c r="D553" t="s">
         <v>148</v>
@@ -8978,10 +8981,10 @@
         <v>232</v>
       </c>
       <c r="B554" s="3">
-        <v>4660</v>
+        <v>4642</v>
       </c>
       <c r="C554" s="6">
-        <v>20.25</v>
+        <v>16.5</v>
       </c>
       <c r="D554" t="s">
         <v>148</v>
@@ -8991,11 +8994,11 @@
       <c r="A555" t="s">
         <v>232</v>
       </c>
-      <c r="B555" s="3">
-        <v>6630</v>
+      <c r="B555" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C555" s="6">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="D555" t="s">
         <v>148</v>
@@ -9006,10 +9009,10 @@
         <v>232</v>
       </c>
       <c r="B556" s="3">
-        <v>6642</v>
+        <v>4660</v>
       </c>
       <c r="C556" s="6">
-        <v>18.5</v>
+        <v>20.25</v>
       </c>
       <c r="D556" t="s">
         <v>148</v>
@@ -9019,11 +9022,11 @@
       <c r="A557" t="s">
         <v>232</v>
       </c>
-      <c r="B557" s="3" t="s">
-        <v>99</v>
+      <c r="B557" s="3">
+        <v>6630</v>
       </c>
       <c r="C557" s="6">
-        <v>103.5</v>
+        <v>19</v>
       </c>
       <c r="D557" t="s">
         <v>148</v>
@@ -9034,10 +9037,10 @@
         <v>232</v>
       </c>
       <c r="B558" s="3">
-        <v>6660</v>
+        <v>6642</v>
       </c>
       <c r="C558" s="6">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="D558" t="s">
         <v>148</v>
@@ -9048,10 +9051,10 @@
         <v>232</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C559" s="6">
-        <v>126</v>
+        <v>103.5</v>
       </c>
       <c r="D559" t="s">
         <v>148</v>
@@ -9062,10 +9065,10 @@
         <v>232</v>
       </c>
       <c r="B560" s="3">
-        <v>8860</v>
+        <v>6660</v>
       </c>
       <c r="C560" s="6">
-        <v>42.25</v>
+        <v>22.5</v>
       </c>
       <c r="D560" t="s">
         <v>148</v>
@@ -9076,27 +9079,27 @@
         <v>232</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>316</v>
+        <v>100</v>
       </c>
       <c r="C561" s="6">
-        <v>5.75</v>
+        <v>126</v>
       </c>
       <c r="D561" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>232</v>
       </c>
-      <c r="B562" s="3" t="s">
-        <v>317</v>
+      <c r="B562" s="3">
+        <v>8860</v>
       </c>
       <c r="C562" s="6">
-        <v>20</v>
+        <v>42.25</v>
       </c>
       <c r="D562" t="s">
-        <v>309</v>
+        <v>148</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
@@ -9104,10 +9107,10 @@
         <v>232</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C563" s="6">
-        <v>12.5</v>
+        <v>5.75</v>
       </c>
       <c r="D563" t="s">
         <v>309</v>
@@ -9118,10 +9121,10 @@
         <v>232</v>
       </c>
       <c r="B564" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C564" s="6">
-        <v>77.5</v>
+        <v>20</v>
       </c>
       <c r="D564" t="s">
         <v>309</v>
@@ -9132,41 +9135,41 @@
         <v>232</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C565" s="6">
-        <v>195</v>
+        <v>12.5</v>
       </c>
       <c r="D565" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A569" t="s">
-        <v>276</v>
-      </c>
-      <c r="B569" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C569" s="6">
-        <v>50.35</v>
-      </c>
-      <c r="D569" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A570" t="s">
-        <v>276</v>
-      </c>
-      <c r="B570" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C570" s="6">
-        <v>41.99</v>
-      </c>
-      <c r="D570" t="s">
-        <v>150</v>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>232</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C566" s="6">
+        <v>77.5</v>
+      </c>
+      <c r="D566" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>232</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C567" s="6">
+        <v>195</v>
+      </c>
+      <c r="D567" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
@@ -9174,13 +9177,13 @@
         <v>276</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C571" s="6">
-        <v>82</v>
+        <v>50.35</v>
       </c>
       <c r="D571" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
@@ -9188,13 +9191,13 @@
         <v>276</v>
       </c>
       <c r="B572" s="3" t="s">
-        <v>256</v>
+        <v>104</v>
       </c>
       <c r="C572" s="6">
-        <v>28</v>
+        <v>41.99</v>
       </c>
       <c r="D572" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
@@ -9202,13 +9205,13 @@
         <v>276</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="C573" s="6">
-        <v>28.05</v>
+        <v>82</v>
       </c>
       <c r="D573" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.25">
@@ -9216,13 +9219,13 @@
         <v>276</v>
       </c>
       <c r="B574" s="3" t="s">
-        <v>113</v>
+        <v>256</v>
       </c>
       <c r="C574" s="6">
-        <v>28.05</v>
+        <v>28</v>
       </c>
       <c r="D574" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.25">
@@ -9230,7 +9233,7 @@
         <v>276</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C575" s="6">
         <v>28.05</v>
@@ -9244,41 +9247,41 @@
         <v>276</v>
       </c>
       <c r="B576" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C576" s="6">
-        <v>11.2</v>
+        <v>28.05</v>
       </c>
       <c r="D576" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A579" t="s">
-        <v>144</v>
-      </c>
-      <c r="B579" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C579" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="D579" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A580" t="s">
-        <v>144</v>
-      </c>
-      <c r="B580" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C580" s="6">
-        <v>199</v>
-      </c>
-      <c r="D580" t="s">
-        <v>139</v>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>276</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C577" s="6">
+        <v>28.05</v>
+      </c>
+      <c r="D577" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>276</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C578" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D578" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
@@ -9286,13 +9289,13 @@
         <v>144</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C581" s="6">
-        <v>175</v>
+        <v>29.87</v>
       </c>
       <c r="D581" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
@@ -9300,13 +9303,13 @@
         <v>144</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C582" s="6">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D582" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
@@ -9314,10 +9317,10 @@
         <v>144</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C583" s="6">
-        <v>309</v>
+        <v>175</v>
       </c>
       <c r="D583" t="s">
         <v>142</v>
@@ -9328,13 +9331,13 @@
         <v>144</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="C584" s="6">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D584" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.25">
@@ -9342,13 +9345,13 @@
         <v>144</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>202</v>
+        <v>31</v>
       </c>
       <c r="C585" s="6">
-        <v>134</v>
+        <v>309</v>
       </c>
       <c r="D585" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.25">
@@ -9356,13 +9359,13 @@
         <v>144</v>
       </c>
       <c r="B586" s="3" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="C586" s="6">
-        <v>59.99</v>
+        <v>175</v>
       </c>
       <c r="D586" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.25">
@@ -9370,13 +9373,13 @@
         <v>144</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="C587" s="6">
-        <v>32.99</v>
+        <v>134</v>
       </c>
       <c r="D587" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.25">
@@ -9384,10 +9387,10 @@
         <v>144</v>
       </c>
       <c r="B588" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C588" s="6">
-        <v>129</v>
+        <v>59.99</v>
       </c>
       <c r="D588" t="s">
         <v>145</v>
@@ -9398,10 +9401,10 @@
         <v>144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C589" s="6">
-        <v>149.99</v>
+        <v>32.99</v>
       </c>
       <c r="D589" t="s">
         <v>145</v>
@@ -9412,13 +9415,13 @@
         <v>144</v>
       </c>
       <c r="B590" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C590" s="6">
-        <v>47.99</v>
+        <v>129</v>
       </c>
       <c r="D590" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.25">
@@ -9426,13 +9429,13 @@
         <v>144</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="C591" s="6">
-        <v>39.99</v>
+        <v>149.99</v>
       </c>
       <c r="D591" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.25">
@@ -9440,13 +9443,13 @@
         <v>144</v>
       </c>
       <c r="B592" s="3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="C592" s="6">
-        <v>39.99</v>
+        <v>47.99</v>
       </c>
       <c r="D592" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
@@ -9454,10 +9457,13 @@
         <v>144</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>106</v>
+        <v>64</v>
+      </c>
+      <c r="C593" s="6">
+        <v>39.99</v>
       </c>
       <c r="D593" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
@@ -9465,41 +9471,38 @@
         <v>144</v>
       </c>
       <c r="B594" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C594" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D594" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>144</v>
+      </c>
+      <c r="B595" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D595" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>144</v>
+      </c>
+      <c r="B596" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C594" s="6">
+      <c r="C596" s="6">
         <v>36.950000000000003</v>
       </c>
-      <c r="D594" t="s">
+      <c r="D596" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A597" t="s">
-        <v>288</v>
-      </c>
-      <c r="B597" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C597" s="6">
-        <v>18</v>
-      </c>
-      <c r="D597" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A598" t="s">
-        <v>288</v>
-      </c>
-      <c r="B598" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C598" s="6">
-        <v>100</v>
-      </c>
-      <c r="D598" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.25">
@@ -9507,10 +9510,10 @@
         <v>288</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C599" s="6">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D599" t="s">
         <v>139</v>
@@ -9521,10 +9524,10 @@
         <v>288</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C600" s="6">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D600" t="s">
         <v>139</v>
@@ -9535,10 +9538,10 @@
         <v>288</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C601" s="6">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="D601" t="s">
         <v>139</v>
@@ -9549,10 +9552,10 @@
         <v>288</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C602" s="6">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D602" t="s">
         <v>139</v>
@@ -9563,10 +9566,10 @@
         <v>288</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C603" s="6">
-        <v>239</v>
+        <v>185</v>
       </c>
       <c r="D603" t="s">
         <v>139</v>
@@ -9577,10 +9580,10 @@
         <v>288</v>
       </c>
       <c r="B604" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C604" s="6">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="D604" t="s">
         <v>139</v>
@@ -9591,10 +9594,10 @@
         <v>288</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C605" s="6">
-        <v>189</v>
+        <v>239</v>
       </c>
       <c r="D605" t="s">
         <v>139</v>
@@ -9605,10 +9608,10 @@
         <v>288</v>
       </c>
       <c r="B606" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C606" s="6">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D606" t="s">
         <v>139</v>
@@ -9619,10 +9622,10 @@
         <v>288</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C607" s="6">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D607" t="s">
         <v>139</v>
@@ -9633,10 +9636,10 @@
         <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C608" s="6">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="D608" t="s">
         <v>139</v>
@@ -9647,13 +9650,13 @@
         <v>288</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C609" s="6">
-        <v>19.989999999999998</v>
+        <v>285</v>
       </c>
       <c r="D609" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
@@ -9661,13 +9664,13 @@
         <v>288</v>
       </c>
       <c r="B610" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C610" s="6">
-        <v>29.99</v>
+        <v>250</v>
       </c>
       <c r="D610" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.25">
@@ -9675,13 +9678,13 @@
         <v>288</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C611" s="6">
-        <v>155</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="D611" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.25">
@@ -9689,13 +9692,13 @@
         <v>288</v>
       </c>
       <c r="B612" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C612" s="6">
-        <v>190</v>
+        <v>29.99</v>
       </c>
       <c r="D612" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
@@ -9703,10 +9706,10 @@
         <v>288</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C613" s="6">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="D613" t="s">
         <v>142</v>
@@ -9717,10 +9720,10 @@
         <v>288</v>
       </c>
       <c r="B614" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C614" s="6">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D614" t="s">
         <v>142</v>
@@ -9731,10 +9734,10 @@
         <v>288</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C615" s="6">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D615" t="s">
         <v>142</v>
@@ -9745,10 +9748,10 @@
         <v>288</v>
       </c>
       <c r="B616" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C616" s="6">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="D616" t="s">
         <v>142</v>
@@ -9759,10 +9762,10 @@
         <v>288</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C617" s="6">
-        <v>389</v>
+        <v>199</v>
       </c>
       <c r="D617" t="s">
         <v>142</v>
@@ -9773,10 +9776,10 @@
         <v>288</v>
       </c>
       <c r="B618" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C618" s="6">
-        <v>399.99</v>
+        <v>260</v>
       </c>
       <c r="D618" t="s">
         <v>142</v>
@@ -9787,10 +9790,10 @@
         <v>288</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C619" s="6">
-        <v>89.23</v>
+        <v>389</v>
       </c>
       <c r="D619" t="s">
         <v>142</v>
@@ -9800,14 +9803,14 @@
       <c r="A620" t="s">
         <v>288</v>
       </c>
-      <c r="B620" s="3">
-        <v>6102</v>
+      <c r="B620" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C620" s="6">
-        <v>44</v>
+        <v>399.99</v>
       </c>
       <c r="D620" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.25">
@@ -9815,27 +9818,27 @@
         <v>288</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
       <c r="C621" s="6">
-        <v>64</v>
+        <v>89.23</v>
       </c>
       <c r="D621" t="s">
-        <v>269</v>
+        <v>142</v>
       </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>288</v>
       </c>
-      <c r="B622" s="3" t="s">
-        <v>282</v>
+      <c r="B622" s="3">
+        <v>6102</v>
       </c>
       <c r="C622" s="6">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D622" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.25">
@@ -9843,10 +9846,10 @@
         <v>288</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C623" s="6">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D623" t="s">
         <v>269</v>
@@ -9857,10 +9860,10 @@
         <v>288</v>
       </c>
       <c r="B624" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C624" s="6">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D624" t="s">
         <v>269</v>
@@ -9871,10 +9874,10 @@
         <v>288</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C625" s="6">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D625" t="s">
         <v>269</v>
@@ -9885,10 +9888,10 @@
         <v>288</v>
       </c>
       <c r="B626" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C626" s="6">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D626" t="s">
         <v>269</v>
@@ -9899,13 +9902,13 @@
         <v>288</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>55</v>
+        <v>285</v>
       </c>
       <c r="C627" s="6">
-        <v>27.99</v>
+        <v>90</v>
       </c>
       <c r="D627" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.25">
@@ -9913,13 +9916,13 @@
         <v>288</v>
       </c>
       <c r="B628" s="3" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="C628" s="6">
-        <v>28.99</v>
+        <v>114</v>
       </c>
       <c r="D628" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.25">
@@ -9927,10 +9930,10 @@
         <v>288</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C629" s="6">
-        <v>39.99</v>
+        <v>27.99</v>
       </c>
       <c r="D629" t="s">
         <v>145</v>
@@ -9941,10 +9944,10 @@
         <v>288</v>
       </c>
       <c r="B630" s="3" t="s">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="C630" s="6">
-        <v>58</v>
+        <v>28.99</v>
       </c>
       <c r="D630" t="s">
         <v>145</v>
@@ -9955,10 +9958,10 @@
         <v>288</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>256</v>
+        <v>56</v>
       </c>
       <c r="C631" s="6">
-        <v>42.99</v>
+        <v>39.99</v>
       </c>
       <c r="D631" t="s">
         <v>145</v>
@@ -9969,10 +9972,10 @@
         <v>288</v>
       </c>
       <c r="B632" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C632" s="6">
         <v>58</v>
-      </c>
-      <c r="C632" s="6">
-        <v>129</v>
       </c>
       <c r="D632" t="s">
         <v>145</v>
@@ -9983,10 +9986,10 @@
         <v>288</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C633" s="6">
-        <v>180</v>
+        <v>42.99</v>
       </c>
       <c r="D633" t="s">
         <v>145</v>
@@ -9997,13 +10000,13 @@
         <v>288</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C634" s="6">
-        <v>54.5</v>
+        <v>129</v>
       </c>
       <c r="D634" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.25">
@@ -10011,13 +10014,13 @@
         <v>288</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>64</v>
+        <v>257</v>
       </c>
       <c r="C635" s="6">
-        <v>48.99</v>
+        <v>180</v>
       </c>
       <c r="D635" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.25">
@@ -10025,10 +10028,10 @@
         <v>288</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C636" s="6">
-        <v>39.99</v>
+        <v>54.5</v>
       </c>
       <c r="D636" t="s">
         <v>146</v>
@@ -10039,10 +10042,10 @@
         <v>288</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C637" s="6">
-        <v>64.989999999999995</v>
+        <v>48.99</v>
       </c>
       <c r="D637" t="s">
         <v>146</v>
@@ -10053,10 +10056,10 @@
         <v>288</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C638" s="6">
-        <v>29.99</v>
+        <v>39.99</v>
       </c>
       <c r="D638" t="s">
         <v>146</v>
@@ -10067,10 +10070,10 @@
         <v>288</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C639" s="6">
-        <v>28.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="D639" t="s">
         <v>146</v>
@@ -10081,7 +10084,10 @@
         <v>288</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>176</v>
+        <v>60</v>
+      </c>
+      <c r="C640" s="6">
+        <v>29.99</v>
       </c>
       <c r="D640" t="s">
         <v>146</v>
@@ -10092,10 +10098,10 @@
         <v>288</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C641" s="6">
-        <v>29.99</v>
+        <v>28.99</v>
       </c>
       <c r="D641" t="s">
         <v>146</v>
@@ -10106,10 +10112,7 @@
         <v>288</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C642" s="6">
-        <v>25.99</v>
+        <v>176</v>
       </c>
       <c r="D642" t="s">
         <v>146</v>
@@ -10119,14 +10122,14 @@
       <c r="A643" t="s">
         <v>288</v>
       </c>
-      <c r="B643" s="3">
-        <v>6642</v>
+      <c r="B643" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C643" s="6">
-        <v>50</v>
+        <v>29.99</v>
       </c>
       <c r="D643" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.25">
@@ -10134,27 +10137,27 @@
         <v>288</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="C644" s="6">
-        <v>40</v>
+        <v>25.99</v>
       </c>
       <c r="D644" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>288</v>
       </c>
-      <c r="B645" s="3" t="s">
-        <v>111</v>
+      <c r="B645" s="3">
+        <v>6642</v>
       </c>
       <c r="C645" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D645" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.25">
@@ -10162,13 +10165,13 @@
         <v>288</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C646" s="6">
-        <v>39.99</v>
+        <v>40</v>
       </c>
       <c r="D646" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.25">
@@ -10176,41 +10179,41 @@
         <v>288</v>
       </c>
       <c r="B647" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C647" s="6">
+        <v>40</v>
+      </c>
+      <c r="D647" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A648" t="s">
+        <v>288</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C648" s="6">
+        <v>39.99</v>
+      </c>
+      <c r="D648" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A649" t="s">
+        <v>288</v>
+      </c>
+      <c r="B649" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C647" s="6">
+      <c r="C649" s="6">
         <v>90</v>
       </c>
-      <c r="D647" t="s">
+      <c r="D649" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A650" t="s">
-        <v>290</v>
-      </c>
-      <c r="B650" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C650" s="6">
-        <v>42.75</v>
-      </c>
-      <c r="D650" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A651" t="s">
-        <v>290</v>
-      </c>
-      <c r="B651" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C651" s="6">
-        <v>68</v>
-      </c>
-      <c r="D651" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.25">
@@ -10218,150 +10221,150 @@
         <v>290</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C652" s="6">
-        <v>82.2</v>
+        <v>42.75</v>
       </c>
       <c r="D652" t="s">
         <v>139</v>
       </c>
     </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A653" t="s">
+        <v>290</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C653" s="6">
+        <v>68</v>
+      </c>
+      <c r="D653" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="C654" s="6">
-        <v>10</v>
+        <v>82.2</v>
       </c>
       <c r="D654" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A655" t="s">
-        <v>304</v>
-      </c>
-      <c r="B655" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D655" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>304</v>
       </c>
-      <c r="B656" s="3">
-        <v>4642</v>
+      <c r="B656" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C656" s="6">
-        <v>18.96</v>
+        <v>10</v>
       </c>
       <c r="D656" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>304</v>
       </c>
-      <c r="B657" s="3">
-        <v>6642</v>
-      </c>
-      <c r="C657" s="6">
-        <v>22.37</v>
+      <c r="B657" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D657" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>304</v>
       </c>
-      <c r="B658" s="3" t="s">
-        <v>116</v>
+      <c r="B658" s="3">
+        <v>4642</v>
       </c>
       <c r="C658" s="6">
-        <v>9.1</v>
+        <v>18.96</v>
       </c>
       <c r="D658" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>304</v>
       </c>
-      <c r="B659" s="3" t="s">
+      <c r="B659" s="3">
+        <v>6642</v>
+      </c>
+      <c r="C659" s="6">
+        <v>22.37</v>
+      </c>
+      <c r="D659" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A660" t="s">
+        <v>304</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C660" s="6">
+        <v>9.1</v>
+      </c>
+      <c r="D660" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A661" t="s">
+        <v>304</v>
+      </c>
+      <c r="B661" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C659" s="6">
+      <c r="C661" s="6">
         <v>9.1</v>
       </c>
-      <c r="D659" t="s">
+      <c r="D661" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A664" t="s">
+    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A666" t="s">
         <v>292</v>
       </c>
-      <c r="B664" s="3" t="s">
+      <c r="B666" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C664" s="6">
+      <c r="C666" s="6">
         <v>5</v>
       </c>
-      <c r="D664" t="s">
+      <c r="D666" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A665" t="s">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A667" t="s">
         <v>292</v>
       </c>
-      <c r="B665" s="3" t="s">
+      <c r="B667" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C665" s="6">
+      <c r="C667" s="6">
         <v>5</v>
       </c>
-      <c r="D665" t="s">
+      <c r="D667" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A669" t="s">
-        <v>293</v>
-      </c>
-      <c r="B669" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C669" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D669" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A670" t="s">
-        <v>293</v>
-      </c>
-      <c r="B670" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C670" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="D670" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
@@ -10369,10 +10372,10 @@
         <v>293</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C671" s="6">
-        <v>8.1</v>
+        <v>3.15</v>
       </c>
       <c r="D671" t="s">
         <v>303</v>
@@ -10383,10 +10386,10 @@
         <v>293</v>
       </c>
       <c r="B672" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C672" s="6">
-        <v>10.8</v>
+        <v>7.65</v>
       </c>
       <c r="D672" t="s">
         <v>303</v>
@@ -10397,10 +10400,10 @@
         <v>293</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C673" s="6">
-        <v>12.2</v>
+        <v>8.1</v>
       </c>
       <c r="D673" t="s">
         <v>303</v>
@@ -10411,10 +10414,10 @@
         <v>293</v>
       </c>
       <c r="B674" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C674" s="6">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="D674" t="s">
         <v>303</v>
@@ -10425,10 +10428,10 @@
         <v>293</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C675" s="6">
-        <v>11.25</v>
+        <v>12.2</v>
       </c>
       <c r="D675" t="s">
         <v>303</v>
@@ -10439,7 +10442,7 @@
         <v>293</v>
       </c>
       <c r="B676" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C676" s="6">
         <v>11.25</v>
@@ -10448,31 +10451,31 @@
         <v>303</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A679" t="s">
-        <v>294</v>
-      </c>
-      <c r="B679" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C679" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D679" t="s">
+    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A677" t="s">
+        <v>293</v>
+      </c>
+      <c r="B677" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C677" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D677" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A680" t="s">
-        <v>294</v>
-      </c>
-      <c r="B680" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C680" s="6">
-        <v>10.19</v>
-      </c>
-      <c r="D680" t="s">
+    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A678" t="s">
+        <v>293</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C678" s="6">
+        <v>11.25</v>
+      </c>
+      <c r="D678" t="s">
         <v>303</v>
       </c>
     </row>
@@ -10481,10 +10484,10 @@
         <v>294</v>
       </c>
       <c r="B681" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C681" s="6">
-        <v>14.4</v>
+        <v>3.36</v>
       </c>
       <c r="D681" t="s">
         <v>303</v>
@@ -10495,10 +10498,10 @@
         <v>294</v>
       </c>
       <c r="B682" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C682" s="6">
-        <v>14.39</v>
+        <v>10.19</v>
       </c>
       <c r="D682" t="s">
         <v>303</v>
@@ -10509,10 +10512,10 @@
         <v>294</v>
       </c>
       <c r="B683" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C683" s="6">
-        <v>11.52</v>
+        <v>14.4</v>
       </c>
       <c r="D683" t="s">
         <v>303</v>
@@ -10523,10 +10526,10 @@
         <v>294</v>
       </c>
       <c r="B684" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C684" s="6">
-        <v>12</v>
+        <v>14.39</v>
       </c>
       <c r="D684" t="s">
         <v>303</v>
@@ -10537,10 +10540,10 @@
         <v>294</v>
       </c>
       <c r="B685" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C685" s="6">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="D685" t="s">
         <v>303</v>
@@ -10551,12 +10554,40 @@
         <v>294</v>
       </c>
       <c r="B686" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C686" s="6">
         <v>12</v>
       </c>
       <c r="D686" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A687" t="s">
+        <v>294</v>
+      </c>
+      <c r="B687" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C687" s="6">
+        <v>12</v>
+      </c>
+      <c r="D687" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A688" t="s">
+        <v>294</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C688" s="6">
+        <v>12</v>
+      </c>
+      <c r="D688" t="s">
         <v>303</v>
       </c>
     </row>
